--- a/research/traditional_assets/database/data/italy/italy_retail_special_lines.xlsx
+++ b/research/traditional_assets/database/data/italy/italy_retail_special_lines.xlsx
@@ -1787,7 +1787,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1924,22 +1924,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1167863104086869</v>
+        <v>0.116540223263706</v>
       </c>
       <c r="C2">
-        <v>560.6196248929999</v>
+        <v>556.8378671840053</v>
       </c>
       <c r="D2">
-        <v>539.9196248929999</v>
+        <v>541.7978671840052</v>
       </c>
       <c r="E2">
-        <v>-167.6</v>
+        <v>-161.94</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>5.66</v>
       </c>
       <c r="G2">
         <v>20.7</v>
@@ -1960,28 +1960,28 @@
         <v>14.025</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.284698</v>
       </c>
       <c r="N2">
-        <v>14.025</v>
+        <v>13.740302</v>
       </c>
       <c r="O2">
-        <v>3.366</v>
+        <v>3.297672479999999</v>
       </c>
       <c r="P2">
-        <v>10.659</v>
+        <v>10.44262952</v>
       </c>
       <c r="Q2">
-        <v>29.759</v>
+        <v>29.54262952</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1167863104086869</v>
+        <v>0.1173312558219253</v>
       </c>
       <c r="T2">
-        <v>0.9771532823765238</v>
+        <v>0.9846546611099194</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1998,7 +1998,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>49.26272752179501</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -2006,22 +2006,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.116540223263706</v>
+        <v>0.1162941361187251</v>
       </c>
       <c r="C3">
-        <v>556.8378671840053</v>
+        <v>553.0692229425534</v>
       </c>
       <c r="D3">
-        <v>541.7978671840052</v>
+        <v>543.6892229425534</v>
       </c>
       <c r="E3">
-        <v>-161.94</v>
+        <v>-156.28</v>
       </c>
       <c r="F3">
-        <v>5.66</v>
+        <v>11.32</v>
       </c>
       <c r="G3">
         <v>20.7</v>
@@ -2042,28 +2042,28 @@
         <v>14.025</v>
       </c>
       <c r="M3">
-        <v>0.284698</v>
+        <v>0.569396</v>
       </c>
       <c r="N3">
-        <v>13.740302</v>
+        <v>13.455604</v>
       </c>
       <c r="O3">
-        <v>3.297672479999999</v>
+        <v>3.22934496</v>
       </c>
       <c r="P3">
-        <v>10.44262952</v>
+        <v>10.22625904</v>
       </c>
       <c r="Q3">
-        <v>29.54262952</v>
+        <v>29.32625904</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1173312558219253</v>
+        <v>0.1178873225701277</v>
       </c>
       <c r="T3">
-        <v>0.9846546611099194</v>
+        <v>0.9923091292052209</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>49.26272752179501</v>
+        <v>24.63136376089751</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -2088,22 +2088,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1162941361187251</v>
+        <v>0.1160480489737443</v>
       </c>
       <c r="C4">
-        <v>553.0692229425534</v>
+        <v>549.3138299826833</v>
       </c>
       <c r="D4">
-        <v>543.6892229425534</v>
+        <v>545.5938299826832</v>
       </c>
       <c r="E4">
-        <v>-156.28</v>
+        <v>-150.62</v>
       </c>
       <c r="F4">
-        <v>11.32</v>
+        <v>16.98</v>
       </c>
       <c r="G4">
         <v>20.7</v>
@@ -2124,28 +2124,28 @@
         <v>14.025</v>
       </c>
       <c r="M4">
-        <v>0.569396</v>
+        <v>0.854094</v>
       </c>
       <c r="N4">
-        <v>13.455604</v>
+        <v>13.170906</v>
       </c>
       <c r="O4">
-        <v>3.22934496</v>
+        <v>3.16101744</v>
       </c>
       <c r="P4">
-        <v>10.22625904</v>
+        <v>10.00988856</v>
       </c>
       <c r="Q4">
-        <v>29.32625904</v>
+        <v>29.10988856</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1178873225701277</v>
+        <v>0.1184548546121076</v>
       </c>
       <c r="T4">
-        <v>0.9923091292052209</v>
+        <v>1.000121421384962</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>24.63136376089751</v>
+        <v>16.42090917393167</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -2170,22 +2170,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1160480489737443</v>
+        <v>0.1158475618287635</v>
       </c>
       <c r="C5">
-        <v>549.3138299826833</v>
+        <v>545.2154053814072</v>
       </c>
       <c r="D5">
-        <v>545.5938299826832</v>
+        <v>547.1554053814071</v>
       </c>
       <c r="E5">
-        <v>-150.62</v>
+        <v>-144.96</v>
       </c>
       <c r="F5">
-        <v>16.98</v>
+        <v>22.64</v>
       </c>
       <c r="G5">
         <v>20.7</v>
@@ -2206,45 +2206,45 @@
         <v>14.025</v>
       </c>
       <c r="M5">
-        <v>0.854094</v>
+        <v>1.172752</v>
       </c>
       <c r="N5">
-        <v>13.170906</v>
+        <v>12.852248</v>
       </c>
       <c r="O5">
-        <v>3.16101744</v>
+        <v>3.08453952</v>
       </c>
       <c r="P5">
-        <v>10.00988856</v>
+        <v>9.76770848</v>
       </c>
       <c r="Q5">
-        <v>29.10988856</v>
+        <v>28.86770848</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1184548546121076</v>
+        <v>0.1190342102382953</v>
       </c>
       <c r="T5">
-        <v>1.000121421384962</v>
+        <v>1.00809646965178</v>
       </c>
       <c r="U5">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V5">
         <v>0.24</v>
       </c>
       <c r="W5">
-        <v>0.038228</v>
+        <v>0.039368</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y5">
-        <v>16.42090917393167</v>
+        <v>11.95905016576395</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -2252,22 +2252,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1158475618287635</v>
+        <v>0.1156774746837826</v>
       </c>
       <c r="C6">
-        <v>545.2154053814072</v>
+        <v>540.8872236988739</v>
       </c>
       <c r="D6">
-        <v>547.1554053814071</v>
+        <v>548.4872236988738</v>
       </c>
       <c r="E6">
-        <v>-144.96</v>
+        <v>-139.3</v>
       </c>
       <c r="F6">
-        <v>22.64</v>
+        <v>28.3</v>
       </c>
       <c r="G6">
         <v>20.7</v>
@@ -2288,45 +2288,45 @@
         <v>14.025</v>
       </c>
       <c r="M6">
-        <v>1.172752</v>
+        <v>1.51405</v>
       </c>
       <c r="N6">
-        <v>12.852248</v>
+        <v>12.51095</v>
       </c>
       <c r="O6">
-        <v>3.08453952</v>
+        <v>3.002627999999999</v>
       </c>
       <c r="P6">
-        <v>9.76770848</v>
+        <v>9.508321999999998</v>
       </c>
       <c r="Q6">
-        <v>28.86770848</v>
+        <v>28.608322</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1190342102382953</v>
+        <v>0.1196257628250343</v>
       </c>
       <c r="T6">
-        <v>1.00809646965178</v>
+        <v>1.016239413671585</v>
       </c>
       <c r="U6">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V6">
         <v>0.24</v>
       </c>
       <c r="W6">
-        <v>0.039368</v>
+        <v>0.04066</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y6">
-        <v>11.95905016576395</v>
+        <v>9.263234371387997</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2334,22 +2334,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1156774746837826</v>
+        <v>0.1154557075388018</v>
       </c>
       <c r="C7">
-        <v>540.8872236988739</v>
+        <v>536.9734760873148</v>
       </c>
       <c r="D7">
-        <v>548.4872236988738</v>
+        <v>550.2334760873148</v>
       </c>
       <c r="E7">
-        <v>-139.3</v>
+        <v>-133.64</v>
       </c>
       <c r="F7">
-        <v>28.3</v>
+        <v>33.96</v>
       </c>
       <c r="G7">
         <v>20.7</v>
@@ -2370,28 +2370,28 @@
         <v>14.025</v>
       </c>
       <c r="M7">
-        <v>1.51405</v>
+        <v>1.81686</v>
       </c>
       <c r="N7">
-        <v>12.51095</v>
+        <v>12.20814</v>
       </c>
       <c r="O7">
-        <v>3.002627999999999</v>
+        <v>2.9299536</v>
       </c>
       <c r="P7">
-        <v>9.508321999999998</v>
+        <v>9.278186399999999</v>
       </c>
       <c r="Q7">
-        <v>28.608322</v>
+        <v>28.3781864</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1196257628250343</v>
+        <v>0.1202299016370232</v>
       </c>
       <c r="T7">
-        <v>1.016239413671585</v>
+        <v>1.02455561181947</v>
       </c>
       <c r="U7">
         <v>0.0535</v>
@@ -2408,7 +2408,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>9.263234371387997</v>
+        <v>7.719361976156665</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2416,22 +2416,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1154557075388018</v>
+        <v>0.1152765003938209</v>
       </c>
       <c r="C8">
-        <v>536.9734760873148</v>
+        <v>532.7327440378239</v>
       </c>
       <c r="D8">
-        <v>550.2334760873148</v>
+        <v>551.6527440378238</v>
       </c>
       <c r="E8">
-        <v>-133.64</v>
+        <v>-127.98</v>
       </c>
       <c r="F8">
-        <v>33.96</v>
+        <v>39.62</v>
       </c>
       <c r="G8">
         <v>20.7</v>
@@ -2452,45 +2452,45 @@
         <v>14.025</v>
       </c>
       <c r="M8">
-        <v>1.81686</v>
+        <v>2.151366</v>
       </c>
       <c r="N8">
-        <v>12.20814</v>
+        <v>11.873634</v>
       </c>
       <c r="O8">
-        <v>2.9299536</v>
+        <v>2.84967216</v>
       </c>
       <c r="P8">
-        <v>9.278186399999999</v>
+        <v>9.023961839999998</v>
       </c>
       <c r="Q8">
-        <v>28.3781864</v>
+        <v>28.12396184</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1202299016370232</v>
+        <v>0.1208470326815279</v>
       </c>
       <c r="T8">
-        <v>1.02455561181947</v>
+        <v>1.033050652938277</v>
       </c>
       <c r="U8">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V8">
         <v>0.24</v>
       </c>
       <c r="W8">
-        <v>0.04066</v>
+        <v>0.041268</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y8">
-        <v>7.719361976156665</v>
+        <v>6.51911390251589</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2498,22 +2498,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1152765003938209</v>
+        <v>0.1151216132488401</v>
       </c>
       <c r="C9">
-        <v>532.732744037824</v>
+        <v>528.3053166012777</v>
       </c>
       <c r="D9">
-        <v>551.6527440378239</v>
+        <v>552.8853166012776</v>
       </c>
       <c r="E9">
-        <v>-127.98</v>
+        <v>-122.32</v>
       </c>
       <c r="F9">
-        <v>39.62</v>
+        <v>45.28</v>
       </c>
       <c r="G9">
         <v>20.7</v>
@@ -2534,45 +2534,45 @@
         <v>14.025</v>
       </c>
       <c r="M9">
-        <v>2.151366</v>
+        <v>2.503984</v>
       </c>
       <c r="N9">
-        <v>11.873634</v>
+        <v>11.521016</v>
       </c>
       <c r="O9">
-        <v>2.84967216</v>
+        <v>2.76504384</v>
       </c>
       <c r="P9">
-        <v>9.023961839999998</v>
+        <v>8.755972159999999</v>
       </c>
       <c r="Q9">
-        <v>28.12396184</v>
+        <v>27.85597216</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1208470326815279</v>
+        <v>0.1214775796183044</v>
       </c>
       <c r="T9">
-        <v>1.033050652938277</v>
+        <v>1.041730368864016</v>
       </c>
       <c r="U9">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V9">
         <v>0.24</v>
       </c>
       <c r="W9">
-        <v>0.041268</v>
+        <v>0.042028</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y9">
-        <v>6.519113902515889</v>
+        <v>5.60107412826919</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2580,22 +2580,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1151216132488401</v>
+        <v>0.1149135261038592</v>
       </c>
       <c r="C10">
-        <v>528.3053166012777</v>
+        <v>524.3099448371529</v>
       </c>
       <c r="D10">
-        <v>552.8853166012776</v>
+        <v>554.5499448371529</v>
       </c>
       <c r="E10">
-        <v>-122.32</v>
+        <v>-116.66</v>
       </c>
       <c r="F10">
-        <v>45.28</v>
+        <v>50.94</v>
       </c>
       <c r="G10">
         <v>20.7</v>
@@ -2616,28 +2616,28 @@
         <v>14.025</v>
       </c>
       <c r="M10">
-        <v>2.503984</v>
+        <v>2.816982</v>
       </c>
       <c r="N10">
-        <v>11.521016</v>
+        <v>11.208018</v>
       </c>
       <c r="O10">
-        <v>2.76504384</v>
+        <v>2.68992432</v>
       </c>
       <c r="P10">
-        <v>8.755972159999999</v>
+        <v>8.51809368</v>
       </c>
       <c r="Q10">
-        <v>27.85597216</v>
+        <v>27.61809368</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1214775796183044</v>
+        <v>0.1221219847295156</v>
       </c>
       <c r="T10">
-        <v>1.041730368864016</v>
+        <v>1.050600847777133</v>
       </c>
       <c r="U10">
         <v>0.0553</v>
@@ -2654,7 +2654,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>5.60107412826919</v>
+        <v>4.978732558461502</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2662,22 +2662,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1149135261038592</v>
+        <v>0.1148954389588784</v>
       </c>
       <c r="C11">
-        <v>524.3099448371529</v>
+        <v>518.795109632435</v>
       </c>
       <c r="D11">
-        <v>554.5499448371529</v>
+        <v>554.695109632435</v>
       </c>
       <c r="E11">
-        <v>-116.66</v>
+        <v>-111</v>
       </c>
       <c r="F11">
-        <v>50.94</v>
+        <v>56.59999999999999</v>
       </c>
       <c r="G11">
         <v>20.7</v>
@@ -2698,45 +2698,45 @@
         <v>14.025</v>
       </c>
       <c r="M11">
-        <v>2.816982</v>
+        <v>3.27148</v>
       </c>
       <c r="N11">
-        <v>11.208018</v>
+        <v>10.75352</v>
       </c>
       <c r="O11">
-        <v>2.68992432</v>
+        <v>2.580844799999999</v>
       </c>
       <c r="P11">
-        <v>8.51809368</v>
+        <v>8.172675199999999</v>
       </c>
       <c r="Q11">
-        <v>27.61809368</v>
+        <v>27.2726752</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1221219847295156</v>
+        <v>0.1227807099543093</v>
       </c>
       <c r="T11">
-        <v>1.050600847777133</v>
+        <v>1.059668448443875</v>
       </c>
       <c r="U11">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V11">
         <v>0.24</v>
       </c>
       <c r="W11">
-        <v>0.042028</v>
+        <v>0.043928</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y11">
-        <v>4.978732558461502</v>
+        <v>4.287050509249635</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2744,22 +2744,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1148954389588784</v>
+        <v>0.1149989518138975</v>
       </c>
       <c r="C12">
-        <v>518.795109632435</v>
+        <v>512.3053561035432</v>
       </c>
       <c r="D12">
-        <v>554.695109632435</v>
+        <v>553.8653561035431</v>
       </c>
       <c r="E12">
-        <v>-111</v>
+        <v>-105.34</v>
       </c>
       <c r="F12">
-        <v>56.6</v>
+        <v>62.26</v>
       </c>
       <c r="G12">
         <v>20.7</v>
@@ -2780,45 +2780,45 @@
         <v>14.025</v>
       </c>
       <c r="M12">
-        <v>3.27148</v>
+        <v>3.816538</v>
       </c>
       <c r="N12">
-        <v>10.75352</v>
+        <v>10.208462</v>
       </c>
       <c r="O12">
-        <v>2.580844799999999</v>
+        <v>2.450030879999999</v>
       </c>
       <c r="P12">
-        <v>8.172675199999999</v>
+        <v>7.758431119999999</v>
       </c>
       <c r="Q12">
-        <v>27.2726752</v>
+        <v>26.85843112</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1227807099543093</v>
+        <v>0.1234542379931433</v>
       </c>
       <c r="T12">
-        <v>1.059668448443875</v>
+        <v>1.068939815417734</v>
       </c>
       <c r="U12">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V12">
         <v>0.24</v>
       </c>
       <c r="W12">
-        <v>0.043928</v>
+        <v>0.046588</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y12">
-        <v>4.287050509249635</v>
+        <v>3.674796373048034</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2826,22 +2826,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1149989518138975</v>
+        <v>0.1150918246689167</v>
       </c>
       <c r="C13">
-        <v>512.3053561035432</v>
+        <v>505.903002194358</v>
       </c>
       <c r="D13">
-        <v>553.8653561035431</v>
+        <v>553.1230021943579</v>
       </c>
       <c r="E13">
-        <v>-105.34</v>
+        <v>-99.67999999999999</v>
       </c>
       <c r="F13">
-        <v>62.26</v>
+        <v>67.92</v>
       </c>
       <c r="G13">
         <v>20.7</v>
@@ -2862,45 +2862,45 @@
         <v>14.025</v>
       </c>
       <c r="M13">
-        <v>3.816538</v>
+        <v>4.353672</v>
       </c>
       <c r="N13">
-        <v>10.208462</v>
+        <v>9.671327999999999</v>
       </c>
       <c r="O13">
-        <v>2.450030879999999</v>
+        <v>2.32111872</v>
       </c>
       <c r="P13">
-        <v>7.758431119999999</v>
+        <v>7.35020928</v>
       </c>
       <c r="Q13">
-        <v>26.85843112</v>
+        <v>26.45020928</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1234542379931433</v>
+        <v>0.1241430734874053</v>
       </c>
       <c r="T13">
-        <v>1.068939815417734</v>
+        <v>1.078421895277363</v>
       </c>
       <c r="U13">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V13">
         <v>0.24</v>
       </c>
       <c r="W13">
-        <v>0.046588</v>
+        <v>0.048716</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y13">
-        <v>3.674796373048034</v>
+        <v>3.221418609394552</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2908,22 +2908,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1150918246689167</v>
+        <v>0.1157212575239358</v>
       </c>
       <c r="C14">
-        <v>505.903002194358</v>
+        <v>495.2637755217144</v>
       </c>
       <c r="D14">
-        <v>553.1230021943579</v>
+        <v>548.1437755217144</v>
       </c>
       <c r="E14">
-        <v>-99.67999999999999</v>
+        <v>-94.02</v>
       </c>
       <c r="F14">
-        <v>67.92</v>
+        <v>73.58</v>
       </c>
       <c r="G14">
         <v>20.7</v>
@@ -2944,45 +2944,45 @@
         <v>14.025</v>
       </c>
       <c r="M14">
-        <v>4.353672</v>
+        <v>5.290402</v>
       </c>
       <c r="N14">
-        <v>9.671327999999999</v>
+        <v>8.734597999999998</v>
       </c>
       <c r="O14">
-        <v>2.32111872</v>
+        <v>2.096303519999999</v>
       </c>
       <c r="P14">
-        <v>7.35020928</v>
+        <v>6.638294479999999</v>
       </c>
       <c r="Q14">
-        <v>26.45020928</v>
+        <v>25.73829448</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1241430734874053</v>
+        <v>0.124847744280386</v>
       </c>
       <c r="T14">
-        <v>1.078421895277363</v>
+        <v>1.088121953984341</v>
       </c>
       <c r="U14">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V14">
         <v>0.24</v>
       </c>
       <c r="W14">
-        <v>0.048716</v>
+        <v>0.05464400000000001</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y14">
-        <v>3.221418609394552</v>
+        <v>2.651027275431999</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2990,22 +2990,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1157212575239358</v>
+        <v>0.116054290378955</v>
       </c>
       <c r="C15">
-        <v>495.2637755217144</v>
+        <v>487.0053593176891</v>
       </c>
       <c r="D15">
-        <v>548.1437755217144</v>
+        <v>545.5453593176891</v>
       </c>
       <c r="E15">
-        <v>-94.02</v>
+        <v>-88.35999999999999</v>
       </c>
       <c r="F15">
-        <v>73.58</v>
+        <v>79.24000000000001</v>
       </c>
       <c r="G15">
         <v>20.7</v>
@@ -3026,45 +3026,45 @@
         <v>14.025</v>
       </c>
       <c r="M15">
-        <v>5.290402</v>
+        <v>6.006392000000001</v>
       </c>
       <c r="N15">
-        <v>8.734597999999998</v>
+        <v>8.018607999999997</v>
       </c>
       <c r="O15">
-        <v>2.096303519999999</v>
+        <v>1.924465919999999</v>
       </c>
       <c r="P15">
-        <v>6.638294479999999</v>
+        <v>6.094142079999997</v>
       </c>
       <c r="Q15">
-        <v>25.73829448</v>
+        <v>25.19414208</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.124847744280386</v>
+        <v>0.1255688027662267</v>
       </c>
       <c r="T15">
-        <v>1.088121953984341</v>
+        <v>1.098047595451945</v>
       </c>
       <c r="U15">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V15">
         <v>0.24</v>
       </c>
       <c r="W15">
-        <v>0.05464400000000001</v>
+        <v>0.05760800000000001</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y15">
-        <v>2.651027275431999</v>
+        <v>2.335012433420928</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -3072,22 +3072,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.116054290378955</v>
+        <v>0.1160020032339742</v>
       </c>
       <c r="C16">
-        <v>487.0053593176891</v>
+        <v>481.7516868864509</v>
       </c>
       <c r="D16">
-        <v>545.5453593176891</v>
+        <v>545.9516868864508</v>
       </c>
       <c r="E16">
-        <v>-88.35999999999999</v>
+        <v>-82.69999999999999</v>
       </c>
       <c r="F16">
-        <v>79.24000000000001</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="G16">
         <v>20.7</v>
@@ -3108,28 +3108,28 @@
         <v>14.025</v>
       </c>
       <c r="M16">
-        <v>6.006392000000001</v>
+        <v>6.435420000000001</v>
       </c>
       <c r="N16">
-        <v>8.018607999999997</v>
+        <v>7.589579999999998</v>
       </c>
       <c r="O16">
-        <v>1.924465919999999</v>
+        <v>1.821499199999999</v>
       </c>
       <c r="P16">
-        <v>6.094142079999997</v>
+        <v>5.768080799999998</v>
       </c>
       <c r="Q16">
-        <v>25.19414208</v>
+        <v>24.8680808</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1255688027662267</v>
+        <v>0.1263068273340872</v>
       </c>
       <c r="T16">
-        <v>1.098047595451945</v>
+        <v>1.108206781424669</v>
       </c>
       <c r="U16">
         <v>0.07580000000000001</v>
@@ -3146,7 +3146,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>2.335012433420928</v>
+        <v>2.179344937859534</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -3154,22 +3154,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1160020032339741</v>
+        <v>0.1159497160889933</v>
       </c>
       <c r="C17">
-        <v>481.7516868864512</v>
+        <v>476.4986201799309</v>
       </c>
       <c r="D17">
-        <v>545.9516868864512</v>
+        <v>546.3586201799309</v>
       </c>
       <c r="E17">
-        <v>-82.7</v>
+        <v>-77.03999999999999</v>
       </c>
       <c r="F17">
-        <v>84.89999999999999</v>
+        <v>90.56</v>
       </c>
       <c r="G17">
         <v>20.7</v>
@@ -3190,28 +3190,28 @@
         <v>14.025</v>
       </c>
       <c r="M17">
-        <v>6.43542</v>
+        <v>6.864448</v>
       </c>
       <c r="N17">
-        <v>7.589579999999999</v>
+        <v>7.160551999999998</v>
       </c>
       <c r="O17">
-        <v>1.8214992</v>
+        <v>1.718532479999999</v>
       </c>
       <c r="P17">
-        <v>5.768080799999999</v>
+        <v>5.442019519999999</v>
       </c>
       <c r="Q17">
-        <v>24.8680808</v>
+        <v>24.54201952</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1263068273340872</v>
+        <v>0.1270624239154682</v>
       </c>
       <c r="T17">
-        <v>1.108206781424669</v>
+        <v>1.118607852777697</v>
       </c>
       <c r="U17">
         <v>0.07580000000000001</v>
@@ -3228,7 +3228,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>2.179344937859534</v>
+        <v>2.043135879243312</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -3236,22 +3236,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1159497160889933</v>
+        <v>0.1177320689440125</v>
       </c>
       <c r="C18">
-        <v>476.4986201799309</v>
+        <v>457.300793994228</v>
       </c>
       <c r="D18">
-        <v>546.3586201799309</v>
+        <v>532.820793994228</v>
       </c>
       <c r="E18">
-        <v>-77.03999999999999</v>
+        <v>-71.37999999999998</v>
       </c>
       <c r="F18">
-        <v>90.56</v>
+        <v>96.22000000000001</v>
       </c>
       <c r="G18">
         <v>20.7</v>
@@ -3272,45 +3272,45 @@
         <v>14.025</v>
       </c>
       <c r="M18">
-        <v>6.864448</v>
+        <v>8.659800000000001</v>
       </c>
       <c r="N18">
-        <v>7.160551999999998</v>
+        <v>5.365199999999998</v>
       </c>
       <c r="O18">
-        <v>1.718532479999999</v>
+        <v>1.287647999999999</v>
       </c>
       <c r="P18">
-        <v>5.442019519999999</v>
+        <v>4.077551999999999</v>
       </c>
       <c r="Q18">
-        <v>24.54201952</v>
+        <v>23.177552</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1270624239154682</v>
+        <v>0.1278362276433885</v>
       </c>
       <c r="T18">
-        <v>1.118607852777697</v>
+        <v>1.129259552356098</v>
       </c>
       <c r="U18">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V18">
         <v>0.24</v>
       </c>
       <c r="W18">
-        <v>0.05760800000000001</v>
+        <v>0.0684</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y18">
-        <v>2.043135879243312</v>
+        <v>1.619552414605418</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3318,22 +3318,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1177320689440125</v>
+        <v>0.1177877017990316</v>
       </c>
       <c r="C19">
-        <v>457.300793994228</v>
+        <v>451.2290244663409</v>
       </c>
       <c r="D19">
-        <v>532.820793994228</v>
+        <v>532.4090244663408</v>
       </c>
       <c r="E19">
-        <v>-71.37999999999998</v>
+        <v>-65.71999999999998</v>
       </c>
       <c r="F19">
-        <v>96.22000000000001</v>
+        <v>101.88</v>
       </c>
       <c r="G19">
         <v>20.7</v>
@@ -3354,28 +3354,28 @@
         <v>14.025</v>
       </c>
       <c r="M19">
-        <v>8.659800000000001</v>
+        <v>9.1692</v>
       </c>
       <c r="N19">
-        <v>5.365199999999998</v>
+        <v>4.855799999999999</v>
       </c>
       <c r="O19">
-        <v>1.287647999999999</v>
+        <v>1.165392</v>
       </c>
       <c r="P19">
-        <v>4.077551999999999</v>
+        <v>3.690407999999999</v>
       </c>
       <c r="Q19">
-        <v>23.177552</v>
+        <v>22.790408</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1278362276433885</v>
+        <v>0.1286289046329654</v>
       </c>
       <c r="T19">
-        <v>1.129259552356098</v>
+        <v>1.140171049485193</v>
       </c>
       <c r="U19">
         <v>0.09</v>
@@ -3392,7 +3392,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>1.619552414605418</v>
+        <v>1.529577280460673</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3400,22 +3400,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1177877017990316</v>
+        <v>0.1271535963866329</v>
       </c>
       <c r="C20">
-        <v>451.229024466341</v>
+        <v>384.2750310583407</v>
       </c>
       <c r="D20">
-        <v>532.409024466341</v>
+        <v>471.1150310583408</v>
       </c>
       <c r="E20">
-        <v>-65.72</v>
+        <v>-60.05999999999999</v>
       </c>
       <c r="F20">
-        <v>101.88</v>
+        <v>107.54</v>
       </c>
       <c r="G20">
         <v>20.7</v>
@@ -3436,45 +3436,45 @@
         <v>14.025</v>
       </c>
       <c r="M20">
-        <v>9.1692</v>
+        <v>15.786872</v>
       </c>
       <c r="N20">
-        <v>4.855799999999999</v>
+        <v>-1.761872000000004</v>
       </c>
       <c r="O20">
-        <v>1.165392</v>
+        <v>-0.4228492800000009</v>
       </c>
       <c r="P20">
-        <v>3.690407999999999</v>
+        <v>-1.339022720000003</v>
       </c>
       <c r="Q20">
-        <v>22.790408</v>
+        <v>17.76097728</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1286289046329653</v>
+        <v>0.1298871516704493</v>
       </c>
       <c r="T20">
-        <v>1.140171049485192</v>
+        <v>1.157491293566614</v>
       </c>
       <c r="U20">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V20">
-        <v>0.24</v>
+        <v>0.2132151321680444</v>
       </c>
       <c r="W20">
-        <v>0.0684</v>
+        <v>0.1155000185977311</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y20">
-        <v>1.529577280460673</v>
+        <v>0.8883963840335183</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3482,22 +3482,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1271535963866329</v>
+        <v>0.1281635963866329</v>
       </c>
       <c r="C21">
-        <v>384.2750310583407</v>
+        <v>372.8378891868846</v>
       </c>
       <c r="D21">
-        <v>471.1150310583408</v>
+        <v>465.3378891868846</v>
       </c>
       <c r="E21">
-        <v>-60.05999999999999</v>
+        <v>-54.39999999999999</v>
       </c>
       <c r="F21">
-        <v>107.54</v>
+        <v>113.2</v>
       </c>
       <c r="G21">
         <v>20.7</v>
@@ -3518,37 +3518,37 @@
         <v>14.025</v>
       </c>
       <c r="M21">
-        <v>15.786872</v>
+        <v>16.61776</v>
       </c>
       <c r="N21">
-        <v>-1.761872000000004</v>
+        <v>-2.592760000000002</v>
       </c>
       <c r="O21">
-        <v>-0.4228492800000009</v>
+        <v>-0.6222624000000004</v>
       </c>
       <c r="P21">
-        <v>-1.339022720000003</v>
+        <v>-1.970497600000002</v>
       </c>
       <c r="Q21">
-        <v>17.76097728</v>
+        <v>17.1295024</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1298871516704493</v>
+        <v>0.13093824106633</v>
       </c>
       <c r="T21">
-        <v>1.157491293566614</v>
+        <v>1.171959934736197</v>
       </c>
       <c r="U21">
         <v>0.1468</v>
       </c>
       <c r="V21">
-        <v>0.2132151321680444</v>
+        <v>0.2025543755596422</v>
       </c>
       <c r="W21">
-        <v>0.1155000185977311</v>
+        <v>0.1170650176678445</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.8883963840335183</v>
+        <v>0.8439765648318425</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3564,22 +3564,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1281635963866329</v>
+        <v>0.1291735963866329</v>
       </c>
       <c r="C22">
-        <v>372.8378891868846</v>
+        <v>361.540717606817</v>
       </c>
       <c r="D22">
-        <v>465.3378891868846</v>
+        <v>459.700717606817</v>
       </c>
       <c r="E22">
-        <v>-54.39999999999999</v>
+        <v>-48.73999999999998</v>
       </c>
       <c r="F22">
-        <v>113.2</v>
+        <v>118.86</v>
       </c>
       <c r="G22">
         <v>20.7</v>
@@ -3600,37 +3600,37 @@
         <v>14.025</v>
       </c>
       <c r="M22">
-        <v>16.61776</v>
+        <v>17.448648</v>
       </c>
       <c r="N22">
-        <v>-2.592760000000002</v>
+        <v>-3.423648000000004</v>
       </c>
       <c r="O22">
-        <v>-0.6222624000000004</v>
+        <v>-0.8216755200000009</v>
       </c>
       <c r="P22">
-        <v>-1.970497600000002</v>
+        <v>-2.601972480000003</v>
       </c>
       <c r="Q22">
-        <v>17.1295024</v>
+        <v>16.49802752</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.13093824106633</v>
+        <v>0.1320159403203341</v>
       </c>
       <c r="T22">
-        <v>1.171959934736197</v>
+        <v>1.186794870618934</v>
       </c>
       <c r="U22">
         <v>0.1468</v>
       </c>
       <c r="V22">
-        <v>0.2025543755596422</v>
+        <v>0.1929089291044211</v>
       </c>
       <c r="W22">
-        <v>0.1170650176678445</v>
+        <v>0.118480969207471</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.8439765648318425</v>
+        <v>0.8037872046017547</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3646,22 +3646,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1291735963866329</v>
+        <v>0.1428369467252964</v>
       </c>
       <c r="C23">
-        <v>361.540717606817</v>
+        <v>291.1522593487671</v>
       </c>
       <c r="D23">
-        <v>459.700717606817</v>
+        <v>394.9722593487671</v>
       </c>
       <c r="E23">
-        <v>-48.73999999999999</v>
+        <v>-43.08</v>
       </c>
       <c r="F23">
-        <v>118.86</v>
+        <v>124.52</v>
       </c>
       <c r="G23">
         <v>20.7</v>
@@ -3682,45 +3682,45 @@
         <v>14.025</v>
       </c>
       <c r="M23">
-        <v>17.448648</v>
+        <v>25.003616</v>
       </c>
       <c r="N23">
-        <v>-3.423648000000004</v>
+        <v>-10.978616</v>
       </c>
       <c r="O23">
-        <v>-0.8216755200000009</v>
+        <v>-2.634867840000001</v>
       </c>
       <c r="P23">
-        <v>-2.601972480000003</v>
+        <v>-8.343748160000002</v>
       </c>
       <c r="Q23">
-        <v>16.49802752</v>
+        <v>10.75625184</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1320159403203341</v>
+        <v>0.1341127476817019</v>
       </c>
       <c r="T23">
-        <v>1.186794870618934</v>
+        <v>1.2156582131969</v>
       </c>
       <c r="U23">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V23">
-        <v>0.1929089291044211</v>
+        <v>0.1346205284867596</v>
       </c>
       <c r="W23">
-        <v>0.118480969207471</v>
+        <v>0.1737681978798587</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y23">
-        <v>0.8037872046017547</v>
+        <v>0.5609188686948319</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3728,22 +3728,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1428369467252964</v>
+        <v>0.1443869467252964</v>
       </c>
       <c r="C24">
-        <v>291.1522593487671</v>
+        <v>279.2824412914491</v>
       </c>
       <c r="D24">
-        <v>394.9722593487671</v>
+        <v>388.7624412914491</v>
       </c>
       <c r="E24">
-        <v>-43.08</v>
+        <v>-37.41999999999999</v>
       </c>
       <c r="F24">
-        <v>124.52</v>
+        <v>130.18</v>
       </c>
       <c r="G24">
         <v>20.7</v>
@@ -3764,37 +3764,37 @@
         <v>14.025</v>
       </c>
       <c r="M24">
-        <v>25.003616</v>
+        <v>26.140144</v>
       </c>
       <c r="N24">
-        <v>-10.978616</v>
+        <v>-12.115144</v>
       </c>
       <c r="O24">
-        <v>-2.634867840000001</v>
+        <v>-2.907634560000001</v>
       </c>
       <c r="P24">
-        <v>-8.343748160000002</v>
+        <v>-9.207509440000003</v>
       </c>
       <c r="Q24">
-        <v>10.75625184</v>
+        <v>9.892490559999999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1341127476817019</v>
+        <v>0.135259666482763</v>
       </c>
       <c r="T24">
-        <v>1.2156582131969</v>
+        <v>1.231445982199457</v>
       </c>
       <c r="U24">
         <v>0.2008</v>
       </c>
       <c r="V24">
-        <v>0.1346205284867596</v>
+        <v>0.1287674620308136</v>
       </c>
       <c r="W24">
-        <v>0.1737681978798587</v>
+        <v>0.1749434936242126</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.5609188686948319</v>
+        <v>0.5365310917950565</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3810,22 +3810,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1443869467252964</v>
+        <v>0.1459369467252964</v>
       </c>
       <c r="C25">
-        <v>279.2824412914491</v>
+        <v>267.604864326028</v>
       </c>
       <c r="D25">
-        <v>388.7624412914491</v>
+        <v>382.744864326028</v>
       </c>
       <c r="E25">
-        <v>-37.41999999999999</v>
+        <v>-31.75999999999999</v>
       </c>
       <c r="F25">
-        <v>130.18</v>
+        <v>135.84</v>
       </c>
       <c r="G25">
         <v>20.7</v>
@@ -3846,37 +3846,37 @@
         <v>14.025</v>
       </c>
       <c r="M25">
-        <v>26.140144</v>
+        <v>27.276672</v>
       </c>
       <c r="N25">
-        <v>-12.115144</v>
+        <v>-13.251672</v>
       </c>
       <c r="O25">
-        <v>-2.907634560000001</v>
+        <v>-3.18040128</v>
       </c>
       <c r="P25">
-        <v>-9.207509440000003</v>
+        <v>-10.07127072</v>
       </c>
       <c r="Q25">
-        <v>9.892490559999999</v>
+        <v>9.028729279999999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.135259666482763</v>
+        <v>0.1364367673575362</v>
       </c>
       <c r="T25">
-        <v>1.231445982199457</v>
+        <v>1.247649218807344</v>
       </c>
       <c r="U25">
         <v>0.2008</v>
       </c>
       <c r="V25">
-        <v>0.1287674620308136</v>
+        <v>0.123402151112863</v>
       </c>
       <c r="W25">
-        <v>0.1749434936242126</v>
+        <v>0.1760208480565371</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.5365310917950565</v>
+        <v>0.5141756296369293</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3892,22 +3892,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1459369467252964</v>
+        <v>0.1565490029279833</v>
       </c>
       <c r="C26">
-        <v>267.604864326028</v>
+        <v>225.2699516484051</v>
       </c>
       <c r="D26">
-        <v>382.744864326028</v>
+        <v>346.0699516484052</v>
       </c>
       <c r="E26">
-        <v>-31.75999999999999</v>
+        <v>-26.09999999999999</v>
       </c>
       <c r="F26">
-        <v>135.84</v>
+        <v>141.5</v>
       </c>
       <c r="G26">
         <v>20.7</v>
@@ -3928,45 +3928,45 @@
         <v>14.025</v>
       </c>
       <c r="M26">
-        <v>27.276672</v>
+        <v>33.3657</v>
       </c>
       <c r="N26">
-        <v>-13.251672</v>
+        <v>-19.34070000000001</v>
       </c>
       <c r="O26">
-        <v>-3.18040128</v>
+        <v>-4.641768000000001</v>
       </c>
       <c r="P26">
-        <v>-10.07127072</v>
+        <v>-14.698932</v>
       </c>
       <c r="Q26">
-        <v>9.028729279999999</v>
+        <v>4.401067999999997</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1364367673575362</v>
+        <v>0.1380613325258859</v>
       </c>
       <c r="T26">
-        <v>1.247649218807344</v>
+        <v>1.270011969844103</v>
       </c>
       <c r="U26">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>0.123402151112863</v>
+        <v>0.1008820435357268</v>
       </c>
       <c r="W26">
-        <v>0.1760208480565371</v>
+        <v>0.2120120141342756</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y26">
-        <v>0.5141756296369293</v>
+        <v>0.4203418480655283</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3974,22 +3974,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1565490029279833</v>
+        <v>0.1584490029279833</v>
       </c>
       <c r="C27">
-        <v>225.2699516484051</v>
+        <v>213.7729456293431</v>
       </c>
       <c r="D27">
-        <v>346.0699516484052</v>
+        <v>340.2329456293431</v>
       </c>
       <c r="E27">
-        <v>-26.09999999999999</v>
+        <v>-20.44</v>
       </c>
       <c r="F27">
-        <v>141.5</v>
+        <v>147.16</v>
       </c>
       <c r="G27">
         <v>20.7</v>
@@ -4010,37 +4010,37 @@
         <v>14.025</v>
       </c>
       <c r="M27">
-        <v>33.3657</v>
+        <v>34.700328</v>
       </c>
       <c r="N27">
-        <v>-19.34070000000001</v>
+        <v>-20.675328</v>
       </c>
       <c r="O27">
-        <v>-4.641768000000001</v>
+        <v>-4.96207872</v>
       </c>
       <c r="P27">
-        <v>-14.698932</v>
+        <v>-15.71324928</v>
       </c>
       <c r="Q27">
-        <v>4.401067999999997</v>
+        <v>3.386750720000002</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1380613325258859</v>
+        <v>0.1393081072897492</v>
       </c>
       <c r="T27">
-        <v>1.270011969844103</v>
+        <v>1.287174293760915</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.1008820435357268</v>
+        <v>0.09700196493819885</v>
       </c>
       <c r="W27">
-        <v>0.2120120141342756</v>
+        <v>0.2129269366675727</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.4203418480655283</v>
+        <v>0.4041748539091619</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -4056,22 +4056,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1584490029279833</v>
+        <v>0.1603490029279833</v>
       </c>
       <c r="C28">
-        <v>213.7729456293431</v>
+        <v>202.4695739702971</v>
       </c>
       <c r="D28">
-        <v>340.2329456293431</v>
+        <v>334.5895739702972</v>
       </c>
       <c r="E28">
-        <v>-20.44</v>
+        <v>-14.77999999999997</v>
       </c>
       <c r="F28">
-        <v>147.16</v>
+        <v>152.82</v>
       </c>
       <c r="G28">
         <v>20.7</v>
@@ -4092,37 +4092,37 @@
         <v>14.025</v>
       </c>
       <c r="M28">
-        <v>34.700328</v>
+        <v>36.03495600000001</v>
       </c>
       <c r="N28">
-        <v>-20.675328</v>
+        <v>-22.00995600000001</v>
       </c>
       <c r="O28">
-        <v>-4.96207872</v>
+        <v>-5.282389440000002</v>
       </c>
       <c r="P28">
-        <v>-15.71324928</v>
+        <v>-16.72756656000001</v>
       </c>
       <c r="Q28">
-        <v>3.386750720000002</v>
+        <v>2.372433439999995</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1393081072897492</v>
+        <v>0.1405890402663211</v>
       </c>
       <c r="T28">
-        <v>1.287174293760915</v>
+        <v>1.304806818332982</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.09700196493819885</v>
+        <v>0.09340929957011739</v>
       </c>
       <c r="W28">
-        <v>0.2129269366675727</v>
+        <v>0.2137740871613663</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -4130,7 +4130,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.4041748539091619</v>
+        <v>0.3892054148754891</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -4138,22 +4138,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1603490029279833</v>
+        <v>0.1622490029279833</v>
       </c>
       <c r="C29">
-        <v>202.4695739702971</v>
+        <v>191.3503585664802</v>
       </c>
       <c r="D29">
-        <v>334.5895739702972</v>
+        <v>329.1303585664802</v>
       </c>
       <c r="E29">
-        <v>-14.77999999999997</v>
+        <v>-9.119999999999976</v>
       </c>
       <c r="F29">
-        <v>152.82</v>
+        <v>158.48</v>
       </c>
       <c r="G29">
         <v>20.7</v>
@@ -4174,37 +4174,37 @@
         <v>14.025</v>
       </c>
       <c r="M29">
-        <v>36.03495600000001</v>
+        <v>37.369584</v>
       </c>
       <c r="N29">
-        <v>-22.00995600000001</v>
+        <v>-23.344584</v>
       </c>
       <c r="O29">
-        <v>-5.282389440000002</v>
+        <v>-5.602700160000001</v>
       </c>
       <c r="P29">
-        <v>-16.72756656000001</v>
+        <v>-17.74188384</v>
       </c>
       <c r="Q29">
-        <v>2.372433439999995</v>
+        <v>1.358116159999998</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1405890402663211</v>
+        <v>0.1419055547144645</v>
       </c>
       <c r="T29">
-        <v>1.304806818332982</v>
+        <v>1.322929135254274</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.09340929957011739</v>
+        <v>0.09007325315689892</v>
       </c>
       <c r="W29">
-        <v>0.2137740871613663</v>
+        <v>0.2145607269056032</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.3892054148754891</v>
+        <v>0.3753052214870788</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -4220,22 +4220,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1622490029279833</v>
+        <v>0.1641490029279833</v>
       </c>
       <c r="C30">
-        <v>191.3503585664802</v>
+        <v>180.4064299671253</v>
       </c>
       <c r="D30">
-        <v>329.1303585664802</v>
+        <v>323.8464299671253</v>
       </c>
       <c r="E30">
-        <v>-9.119999999999976</v>
+        <v>-3.45999999999998</v>
       </c>
       <c r="F30">
-        <v>158.48</v>
+        <v>164.14</v>
       </c>
       <c r="G30">
         <v>20.7</v>
@@ -4256,37 +4256,37 @@
         <v>14.025</v>
       </c>
       <c r="M30">
-        <v>37.369584</v>
+        <v>38.70421200000001</v>
       </c>
       <c r="N30">
-        <v>-23.344584</v>
+        <v>-24.67921200000001</v>
       </c>
       <c r="O30">
-        <v>-5.602700160000001</v>
+        <v>-5.923010880000001</v>
       </c>
       <c r="P30">
-        <v>-17.74188384</v>
+        <v>-18.75620112000001</v>
       </c>
       <c r="Q30">
-        <v>1.358116159999998</v>
+        <v>0.3437988799999943</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1419055547144645</v>
+        <v>0.14325915407664</v>
       </c>
       <c r="T30">
-        <v>1.322929135254274</v>
+        <v>1.341561939976165</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.09007325315689892</v>
+        <v>0.08696727891010929</v>
       </c>
       <c r="W30">
-        <v>0.2145607269056032</v>
+        <v>0.2152931156329962</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.3753052214870788</v>
+        <v>0.3623636621254555</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4302,22 +4302,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1641490029279833</v>
+        <v>0.1660490029279833</v>
       </c>
       <c r="C31">
-        <v>180.4064299671254</v>
+        <v>169.6294792901535</v>
       </c>
       <c r="D31">
-        <v>323.8464299671254</v>
+        <v>318.7294792901534</v>
       </c>
       <c r="E31">
-        <v>-3.460000000000008</v>
+        <v>2.199999999999989</v>
       </c>
       <c r="F31">
-        <v>164.14</v>
+        <v>169.8</v>
       </c>
       <c r="G31">
         <v>20.7</v>
@@ -4338,37 +4338,37 @@
         <v>14.025</v>
       </c>
       <c r="M31">
-        <v>38.704212</v>
+        <v>40.03884</v>
       </c>
       <c r="N31">
-        <v>-24.679212</v>
+        <v>-26.01384</v>
       </c>
       <c r="O31">
-        <v>-5.92301088</v>
+        <v>-6.2433216</v>
       </c>
       <c r="P31">
-        <v>-18.75620112</v>
+        <v>-19.7705184</v>
       </c>
       <c r="Q31">
-        <v>0.3437988800000014</v>
+        <v>-0.6705183999999988</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.14325915407664</v>
+        <v>0.1446514277063063</v>
       </c>
       <c r="T31">
-        <v>1.341561939976165</v>
+        <v>1.360727110547253</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.0869672789101093</v>
+        <v>0.08406836961310567</v>
       </c>
       <c r="W31">
-        <v>0.2152931156329962</v>
+        <v>0.2159766784452297</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.3623636621254555</v>
+        <v>0.3502848733879402</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4384,22 +4384,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1660490029279833</v>
+        <v>0.1679490029279833</v>
       </c>
       <c r="C32">
-        <v>169.6294792901535</v>
+        <v>159.0117146245807</v>
       </c>
       <c r="D32">
-        <v>318.7294792901534</v>
+        <v>313.7717146245807</v>
       </c>
       <c r="E32">
-        <v>2.199999999999989</v>
+        <v>7.860000000000014</v>
       </c>
       <c r="F32">
-        <v>169.8</v>
+        <v>175.46</v>
       </c>
       <c r="G32">
         <v>20.7</v>
@@ -4420,37 +4420,37 @@
         <v>14.025</v>
       </c>
       <c r="M32">
-        <v>40.03884</v>
+        <v>41.373468</v>
       </c>
       <c r="N32">
-        <v>-26.01384</v>
+        <v>-27.348468</v>
       </c>
       <c r="O32">
-        <v>-6.2433216</v>
+        <v>-6.563632320000001</v>
       </c>
       <c r="P32">
-        <v>-19.7705184</v>
+        <v>-20.78483568</v>
       </c>
       <c r="Q32">
-        <v>-0.6705183999999988</v>
+        <v>-1.684835680000003</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1446514277063063</v>
+        <v>0.1460840570933543</v>
       </c>
       <c r="T32">
-        <v>1.360727110547253</v>
+        <v>1.380447793308808</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.08406836961310567</v>
+        <v>0.08135648672236032</v>
       </c>
       <c r="W32">
-        <v>0.2159766784452297</v>
+        <v>0.2166161404308675</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.3502848733879402</v>
+        <v>0.338985361343168</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4466,22 +4466,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1679490029279833</v>
+        <v>0.1698490029279833</v>
       </c>
       <c r="C33">
-        <v>159.0117146245807</v>
+        <v>148.5458214395077</v>
       </c>
       <c r="D33">
-        <v>313.7717146245807</v>
+        <v>308.9658214395077</v>
       </c>
       <c r="E33">
-        <v>7.860000000000014</v>
+        <v>13.52000000000001</v>
       </c>
       <c r="F33">
-        <v>175.46</v>
+        <v>181.12</v>
       </c>
       <c r="G33">
         <v>20.7</v>
@@ -4502,37 +4502,37 @@
         <v>14.025</v>
       </c>
       <c r="M33">
-        <v>41.373468</v>
+        <v>42.708096</v>
       </c>
       <c r="N33">
-        <v>-27.348468</v>
+        <v>-28.68309600000001</v>
       </c>
       <c r="O33">
-        <v>-6.563632320000001</v>
+        <v>-6.883943040000001</v>
       </c>
       <c r="P33">
-        <v>-20.78483568</v>
+        <v>-21.79915296</v>
       </c>
       <c r="Q33">
-        <v>-1.684835680000003</v>
+        <v>-2.699152960000003</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1460840570933543</v>
+        <v>0.1475588226388447</v>
       </c>
       <c r="T33">
-        <v>1.380447793308808</v>
+        <v>1.400748496151584</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.08135648672236032</v>
+        <v>0.07881409651228655</v>
       </c>
       <c r="W33">
-        <v>0.2166161404308675</v>
+        <v>0.2172156360424028</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.338985361343168</v>
+        <v>0.328392068801194</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4548,22 +4548,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1698490029279833</v>
+        <v>0.1717490029279833</v>
       </c>
       <c r="C34">
-        <v>148.5458214395077</v>
+        <v>138.2249265766025</v>
       </c>
       <c r="D34">
-        <v>308.9658214395077</v>
+        <v>304.3049265766026</v>
       </c>
       <c r="E34">
-        <v>13.52000000000001</v>
+        <v>19.18000000000001</v>
       </c>
       <c r="F34">
-        <v>181.12</v>
+        <v>186.78</v>
       </c>
       <c r="G34">
         <v>20.7</v>
@@ -4584,37 +4584,37 @@
         <v>14.025</v>
       </c>
       <c r="M34">
-        <v>42.708096</v>
+        <v>44.042724</v>
       </c>
       <c r="N34">
-        <v>-28.68309600000001</v>
+        <v>-30.017724</v>
       </c>
       <c r="O34">
-        <v>-6.883943040000001</v>
+        <v>-7.20425376</v>
       </c>
       <c r="P34">
-        <v>-21.79915296</v>
+        <v>-22.81347024</v>
       </c>
       <c r="Q34">
-        <v>-2.699152960000003</v>
+        <v>-3.713470239999999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1475588226388447</v>
+        <v>0.1490776110364394</v>
       </c>
       <c r="T34">
-        <v>1.400748496151584</v>
+        <v>1.421655190123996</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.07881409651228655</v>
+        <v>0.07642579055736878</v>
       </c>
       <c r="W34">
-        <v>0.2172156360424028</v>
+        <v>0.2177787985865725</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.328392068801194</v>
+        <v>0.3184407939890366</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4630,22 +4630,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1717490029279833</v>
+        <v>0.1736490029279833</v>
       </c>
       <c r="C35">
-        <v>138.2249265766025</v>
+        <v>128.0425654532918</v>
       </c>
       <c r="D35">
-        <v>304.3049265766026</v>
+        <v>299.7825654532919</v>
       </c>
       <c r="E35">
-        <v>19.18000000000001</v>
+        <v>24.84000000000003</v>
       </c>
       <c r="F35">
-        <v>186.78</v>
+        <v>192.44</v>
       </c>
       <c r="G35">
         <v>20.7</v>
@@ -4666,37 +4666,37 @@
         <v>14.025</v>
       </c>
       <c r="M35">
-        <v>44.042724</v>
+        <v>45.37735200000001</v>
       </c>
       <c r="N35">
-        <v>-30.017724</v>
+        <v>-31.35235200000001</v>
       </c>
       <c r="O35">
-        <v>-7.20425376</v>
+        <v>-7.524564480000002</v>
       </c>
       <c r="P35">
-        <v>-22.81347024</v>
+        <v>-23.82778752000001</v>
       </c>
       <c r="Q35">
-        <v>-3.713470239999999</v>
+        <v>-4.727787520000007</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1490776110364394</v>
+        <v>0.1506424233248704</v>
       </c>
       <c r="T35">
-        <v>1.421655190123996</v>
+        <v>1.44319542027739</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.07642579055736878</v>
+        <v>0.0741779731880344</v>
       </c>
       <c r="W35">
-        <v>0.2177787985865725</v>
+        <v>0.2183088339222615</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.3184407939890366</v>
+        <v>0.3090748882834766</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4712,22 +4712,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1736490029279833</v>
+        <v>0.1755490029279834</v>
       </c>
       <c r="C36">
-        <v>128.0425654532918</v>
+        <v>117.9926521475425</v>
       </c>
       <c r="D36">
-        <v>299.7825654532919</v>
+        <v>295.3926521475425</v>
       </c>
       <c r="E36">
-        <v>24.84000000000003</v>
+        <v>30.50000000000003</v>
       </c>
       <c r="F36">
-        <v>192.44</v>
+        <v>198.1</v>
       </c>
       <c r="G36">
         <v>20.7</v>
@@ -4748,37 +4748,37 @@
         <v>14.025</v>
       </c>
       <c r="M36">
-        <v>45.37735200000001</v>
+        <v>46.71198</v>
       </c>
       <c r="N36">
-        <v>-31.35235200000001</v>
+        <v>-32.68698000000001</v>
       </c>
       <c r="O36">
-        <v>-7.524564480000002</v>
+        <v>-7.844875200000001</v>
       </c>
       <c r="P36">
-        <v>-23.82778752000001</v>
+        <v>-24.8421048</v>
       </c>
       <c r="Q36">
-        <v>-4.727787520000007</v>
+        <v>-5.742104800000003</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1506424233248704</v>
+        <v>0.1522553836837145</v>
       </c>
       <c r="T36">
-        <v>1.44319542027739</v>
+        <v>1.465398426743196</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.0741779731880344</v>
+        <v>0.07205860252551913</v>
       </c>
       <c r="W36">
-        <v>0.2183088339222615</v>
+        <v>0.2188085815244826</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4786,7 +4786,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.3090748882834766</v>
+        <v>0.3002441771896631</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4794,22 +4794,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1755490029279834</v>
+        <v>0.1774490029279833</v>
       </c>
       <c r="C37">
-        <v>117.9926521475425</v>
+        <v>108.0694520731193</v>
       </c>
       <c r="D37">
-        <v>295.3926521475425</v>
+        <v>291.1294520731194</v>
       </c>
       <c r="E37">
-        <v>30.50000000000003</v>
+        <v>36.16000000000003</v>
       </c>
       <c r="F37">
-        <v>198.1</v>
+        <v>203.76</v>
       </c>
       <c r="G37">
         <v>20.7</v>
@@ -4830,37 +4830,37 @@
         <v>14.025</v>
       </c>
       <c r="M37">
-        <v>46.71198</v>
+        <v>48.04660800000001</v>
       </c>
       <c r="N37">
-        <v>-32.68698000000001</v>
+        <v>-34.02160800000001</v>
       </c>
       <c r="O37">
-        <v>-7.844875200000001</v>
+        <v>-8.165185920000001</v>
       </c>
       <c r="P37">
-        <v>-24.8421048</v>
+        <v>-25.85642208000001</v>
       </c>
       <c r="Q37">
-        <v>-5.742104800000003</v>
+        <v>-6.756422080000007</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1522553836837145</v>
+        <v>0.1539187490537725</v>
       </c>
       <c r="T37">
-        <v>1.465398426743196</v>
+        <v>1.488295277161058</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.07205860252551913</v>
+        <v>0.07005697467758805</v>
       </c>
       <c r="W37">
-        <v>0.2188085815244826</v>
+        <v>0.2192805653710247</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.3002441771896631</v>
+        <v>0.2919040611566168</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4876,22 +4876,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1774490029279833</v>
+        <v>0.1793490029279833</v>
       </c>
       <c r="C38">
-        <v>108.0694520731194</v>
+        <v>98.26755698733407</v>
       </c>
       <c r="D38">
-        <v>291.1294520731194</v>
+        <v>286.9875569873341</v>
       </c>
       <c r="E38">
-        <v>36.16</v>
+        <v>41.81999999999999</v>
       </c>
       <c r="F38">
-        <v>203.76</v>
+        <v>209.42</v>
       </c>
       <c r="G38">
         <v>20.7</v>
@@ -4912,37 +4912,37 @@
         <v>14.025</v>
       </c>
       <c r="M38">
-        <v>48.046608</v>
+        <v>49.381236</v>
       </c>
       <c r="N38">
-        <v>-34.021608</v>
+        <v>-35.356236</v>
       </c>
       <c r="O38">
-        <v>-8.165185919999999</v>
+        <v>-8.485496640000001</v>
       </c>
       <c r="P38">
-        <v>-25.85642208</v>
+        <v>-26.87073936</v>
       </c>
       <c r="Q38">
-        <v>-6.75642208</v>
+        <v>-7.77073936</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1539187490537725</v>
+        <v>0.1556349196736737</v>
       </c>
       <c r="T38">
-        <v>1.488295277161058</v>
+        <v>1.51191901171917</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.07005697467758805</v>
+        <v>0.06816354292954513</v>
       </c>
       <c r="W38">
-        <v>0.2192805653710247</v>
+        <v>0.2197270365772133</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4950,7 +4950,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.2919040611566169</v>
+        <v>0.2840147622064381</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4958,22 +4958,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1793490029279833</v>
+        <v>0.1812490029279833</v>
       </c>
       <c r="C39">
-        <v>98.26755698733407</v>
+        <v>88.58186210225719</v>
       </c>
       <c r="D39">
-        <v>286.9875569873341</v>
+        <v>282.9618621022572</v>
       </c>
       <c r="E39">
-        <v>41.81999999999999</v>
+        <v>47.48000000000002</v>
       </c>
       <c r="F39">
-        <v>209.42</v>
+        <v>215.08</v>
       </c>
       <c r="G39">
         <v>20.7</v>
@@ -4994,37 +4994,37 @@
         <v>14.025</v>
       </c>
       <c r="M39">
-        <v>49.381236</v>
+        <v>50.715864</v>
       </c>
       <c r="N39">
-        <v>-35.356236</v>
+        <v>-36.690864</v>
       </c>
       <c r="O39">
-        <v>-8.485496640000001</v>
+        <v>-8.805807360000001</v>
       </c>
       <c r="P39">
-        <v>-26.87073936</v>
+        <v>-27.88505664</v>
       </c>
       <c r="Q39">
-        <v>-7.77073936</v>
+        <v>-8.785056640000001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1556349196736737</v>
+        <v>0.1574064506361523</v>
       </c>
       <c r="T39">
-        <v>1.51191901171917</v>
+        <v>1.53630480223077</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.06816354292954513</v>
+        <v>0.06636976548403078</v>
       </c>
       <c r="W39">
-        <v>0.2197270365772133</v>
+        <v>0.2201500092988656</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -5032,7 +5032,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.2840147622064381</v>
+        <v>0.2765406895167949</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -5040,22 +5040,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1812490029279833</v>
+        <v>0.1831490029279833</v>
       </c>
       <c r="C40">
-        <v>88.58186210225719</v>
+        <v>79.00754509570299</v>
       </c>
       <c r="D40">
-        <v>282.9618621022572</v>
+        <v>279.047545095703</v>
       </c>
       <c r="E40">
-        <v>47.48000000000002</v>
+        <v>53.14000000000001</v>
       </c>
       <c r="F40">
-        <v>215.08</v>
+        <v>220.74</v>
       </c>
       <c r="G40">
         <v>20.7</v>
@@ -5076,37 +5076,37 @@
         <v>14.025</v>
       </c>
       <c r="M40">
-        <v>50.715864</v>
+        <v>52.05049200000001</v>
       </c>
       <c r="N40">
-        <v>-36.690864</v>
+        <v>-38.02549200000001</v>
       </c>
       <c r="O40">
-        <v>-8.805807360000001</v>
+        <v>-9.126118080000001</v>
       </c>
       <c r="P40">
-        <v>-27.88505664</v>
+        <v>-28.89937392000001</v>
       </c>
       <c r="Q40">
-        <v>-8.785056640000001</v>
+        <v>-9.799373920000004</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1574064506361523</v>
+        <v>0.1592360645810073</v>
       </c>
       <c r="T40">
-        <v>1.53630480223077</v>
+        <v>1.561490126857503</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.06636976548403078</v>
+        <v>0.06466797662546588</v>
       </c>
       <c r="W40">
-        <v>0.2201500092988656</v>
+        <v>0.2205512911117151</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.2765406895167949</v>
+        <v>0.2694499026061079</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -5122,22 +5122,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1831490029279833</v>
+        <v>0.1850490029279833</v>
       </c>
       <c r="C41">
-        <v>79.00754509570299</v>
+        <v>69.54004684053731</v>
       </c>
       <c r="D41">
-        <v>279.047545095703</v>
+        <v>275.2400468405373</v>
       </c>
       <c r="E41">
-        <v>53.14000000000001</v>
+        <v>58.80000000000001</v>
       </c>
       <c r="F41">
-        <v>220.74</v>
+        <v>226.4</v>
       </c>
       <c r="G41">
         <v>20.7</v>
@@ -5158,37 +5158,37 @@
         <v>14.025</v>
       </c>
       <c r="M41">
-        <v>52.05049200000001</v>
+        <v>53.38512</v>
       </c>
       <c r="N41">
-        <v>-38.02549200000001</v>
+        <v>-39.36012</v>
       </c>
       <c r="O41">
-        <v>-9.126118080000001</v>
+        <v>-9.4464288</v>
       </c>
       <c r="P41">
-        <v>-28.89937392000001</v>
+        <v>-29.9136912</v>
       </c>
       <c r="Q41">
-        <v>-9.799373920000004</v>
+        <v>-10.8136912</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1592360645810073</v>
+        <v>0.1611266656573574</v>
       </c>
       <c r="T41">
-        <v>1.561490126857503</v>
+        <v>1.587514962305129</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.06466797662546588</v>
+        <v>0.06305127720982925</v>
       </c>
       <c r="W41">
-        <v>0.2205512911117151</v>
+        <v>0.2209325088339223</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -5196,7 +5196,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.2694499026061079</v>
+        <v>0.2627136550409552</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -5204,22 +5204,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1850490029279833</v>
+        <v>0.1869490029279833</v>
       </c>
       <c r="C42">
-        <v>69.54004684053731</v>
+        <v>60.17505369039915</v>
       </c>
       <c r="D42">
-        <v>275.2400468405373</v>
+        <v>271.5350536903992</v>
       </c>
       <c r="E42">
-        <v>58.80000000000001</v>
+        <v>64.46000000000004</v>
       </c>
       <c r="F42">
-        <v>226.4</v>
+        <v>232.06</v>
       </c>
       <c r="G42">
         <v>20.7</v>
@@ -5240,37 +5240,37 @@
         <v>14.025</v>
       </c>
       <c r="M42">
-        <v>53.38512</v>
+        <v>54.71974800000001</v>
       </c>
       <c r="N42">
-        <v>-39.36012</v>
+        <v>-40.69474800000001</v>
       </c>
       <c r="O42">
-        <v>-9.4464288</v>
+        <v>-9.766739520000002</v>
       </c>
       <c r="P42">
-        <v>-29.9136912</v>
+        <v>-30.92800848000001</v>
       </c>
       <c r="Q42">
-        <v>-10.8136912</v>
+        <v>-11.82800848000001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1611266656573574</v>
+        <v>0.1630813549057872</v>
       </c>
       <c r="T42">
-        <v>1.587514962305129</v>
+        <v>1.614421995564537</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.06305127720982925</v>
+        <v>0.0615134411803212</v>
       </c>
       <c r="W42">
-        <v>0.2209325088339223</v>
+        <v>0.2212951305696803</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.2627136550409552</v>
+        <v>0.256306004918005</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5286,22 +5286,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1869490029279833</v>
+        <v>0.1888490029279833</v>
       </c>
       <c r="C43">
-        <v>60.17505369039915</v>
+        <v>50.90848117712204</v>
       </c>
       <c r="D43">
-        <v>271.5350536903992</v>
+        <v>267.9284811771221</v>
       </c>
       <c r="E43">
-        <v>64.46000000000004</v>
+        <v>70.12000000000003</v>
       </c>
       <c r="F43">
-        <v>232.06</v>
+        <v>237.72</v>
       </c>
       <c r="G43">
         <v>20.7</v>
@@ -5322,37 +5322,37 @@
         <v>14.025</v>
       </c>
       <c r="M43">
-        <v>54.71974800000001</v>
+        <v>56.05437600000001</v>
       </c>
       <c r="N43">
-        <v>-40.69474800000001</v>
+        <v>-42.02937600000001</v>
       </c>
       <c r="O43">
-        <v>-9.766739520000002</v>
+        <v>-10.08705024</v>
       </c>
       <c r="P43">
-        <v>-30.92800848000001</v>
+        <v>-31.94232576000001</v>
       </c>
       <c r="Q43">
-        <v>-11.82800848000001</v>
+        <v>-12.84232576000001</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1630813549057872</v>
+        <v>0.165103447231749</v>
       </c>
       <c r="T43">
-        <v>1.614421995564537</v>
+        <v>1.64225685755703</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.0615134411803212</v>
+        <v>0.0600488354379326</v>
       </c>
       <c r="W43">
-        <v>0.2212951305696803</v>
+        <v>0.2216404846037355</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.256306004918005</v>
+        <v>0.2502034809913859</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5368,22 +5368,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1888490029279833</v>
+        <v>0.1907490029279833</v>
       </c>
       <c r="C44">
-        <v>50.90848117712207</v>
+        <v>41.73645899032954</v>
       </c>
       <c r="D44">
-        <v>267.9284811771221</v>
+        <v>264.4164589903295</v>
       </c>
       <c r="E44">
-        <v>70.12</v>
+        <v>75.78</v>
       </c>
       <c r="F44">
-        <v>237.72</v>
+        <v>243.38</v>
       </c>
       <c r="G44">
         <v>20.7</v>
@@ -5404,37 +5404,37 @@
         <v>14.025</v>
       </c>
       <c r="M44">
-        <v>56.054376</v>
+        <v>57.389004</v>
       </c>
       <c r="N44">
-        <v>-42.02937600000001</v>
+        <v>-43.364004</v>
       </c>
       <c r="O44">
-        <v>-10.08705024</v>
+        <v>-10.40736096</v>
       </c>
       <c r="P44">
-        <v>-31.94232576</v>
+        <v>-32.95664304</v>
       </c>
       <c r="Q44">
-        <v>-12.84232576</v>
+        <v>-13.85664304</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.165103447231749</v>
+        <v>0.1671964901656393</v>
       </c>
       <c r="T44">
-        <v>1.642256857557029</v>
+        <v>1.671068381373819</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.06004883543793262</v>
+        <v>0.05865235089286442</v>
       </c>
       <c r="W44">
-        <v>0.2216404846037355</v>
+        <v>0.2219697756594626</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.2502034809913859</v>
+        <v>0.244384795386935</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5450,22 +5450,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1907490029279833</v>
+        <v>0.1926490029279834</v>
       </c>
       <c r="C45">
-        <v>41.73645899032954</v>
+        <v>32.65531712307413</v>
       </c>
       <c r="D45">
-        <v>264.4164589903295</v>
+        <v>260.9953171230741</v>
       </c>
       <c r="E45">
-        <v>75.78</v>
+        <v>81.44</v>
       </c>
       <c r="F45">
-        <v>243.38</v>
+        <v>249.04</v>
       </c>
       <c r="G45">
         <v>20.7</v>
@@ -5486,37 +5486,37 @@
         <v>14.025</v>
       </c>
       <c r="M45">
-        <v>57.389004</v>
+        <v>58.723632</v>
       </c>
       <c r="N45">
-        <v>-43.364004</v>
+        <v>-44.698632</v>
       </c>
       <c r="O45">
-        <v>-10.40736096</v>
+        <v>-10.72767168</v>
       </c>
       <c r="P45">
-        <v>-32.95664304</v>
+        <v>-33.97096032</v>
       </c>
       <c r="Q45">
-        <v>-13.85664304</v>
+        <v>-14.87096032</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1671964901656393</v>
+        <v>0.1693642846328829</v>
       </c>
       <c r="T45">
-        <v>1.671068381373819</v>
+        <v>1.700908888184066</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.05865235089286442</v>
+        <v>0.05731934291802659</v>
       </c>
       <c r="W45">
-        <v>0.2219697756594626</v>
+        <v>0.2222840989399293</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.244384795386935</v>
+        <v>0.2388305954917774</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5532,22 +5532,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1926490029279834</v>
+        <v>0.1945490029279833</v>
       </c>
       <c r="C46">
-        <v>32.65531712307413</v>
+        <v>23.66157307926417</v>
       </c>
       <c r="D46">
-        <v>260.9953171230741</v>
+        <v>257.6615730792642</v>
       </c>
       <c r="E46">
-        <v>81.44</v>
+        <v>87.10000000000002</v>
       </c>
       <c r="F46">
-        <v>249.04</v>
+        <v>254.7</v>
       </c>
       <c r="G46">
         <v>20.7</v>
@@ -5568,37 +5568,37 @@
         <v>14.025</v>
       </c>
       <c r="M46">
-        <v>58.723632</v>
+        <v>60.05826</v>
       </c>
       <c r="N46">
-        <v>-44.698632</v>
+        <v>-46.03326000000001</v>
       </c>
       <c r="O46">
-        <v>-10.72767168</v>
+        <v>-11.0479824</v>
       </c>
       <c r="P46">
-        <v>-33.97096032</v>
+        <v>-34.9852776</v>
       </c>
       <c r="Q46">
-        <v>-14.87096032</v>
+        <v>-15.8852776</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1693642846328829</v>
+        <v>0.1716109079898444</v>
       </c>
       <c r="T46">
-        <v>1.700908888184066</v>
+        <v>1.731834504332867</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.05731934291802659</v>
+        <v>0.05604557974207044</v>
       </c>
       <c r="W46">
-        <v>0.2222840989399293</v>
+        <v>0.2225844522968198</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.2388305954917774</v>
+        <v>0.2335232489252935</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5614,22 +5614,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1945490029279833</v>
+        <v>0.1964490029279833</v>
       </c>
       <c r="C47">
-        <v>23.66157307926417</v>
+        <v>14.75192004913674</v>
       </c>
       <c r="D47">
-        <v>257.6615730792642</v>
+        <v>254.4119200491367</v>
       </c>
       <c r="E47">
-        <v>87.10000000000002</v>
+        <v>92.76000000000002</v>
       </c>
       <c r="F47">
-        <v>254.7</v>
+        <v>260.36</v>
       </c>
       <c r="G47">
         <v>20.7</v>
@@ -5650,37 +5650,37 @@
         <v>14.025</v>
       </c>
       <c r="M47">
-        <v>60.05826</v>
+        <v>61.39288800000001</v>
       </c>
       <c r="N47">
-        <v>-46.03326000000001</v>
+        <v>-47.36788800000001</v>
       </c>
       <c r="O47">
-        <v>-11.0479824</v>
+        <v>-11.36829312</v>
       </c>
       <c r="P47">
-        <v>-34.9852776</v>
+        <v>-35.99959488</v>
       </c>
       <c r="Q47">
-        <v>-15.8852776</v>
+        <v>-16.89959488</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1716109079898444</v>
+        <v>0.173940739619286</v>
       </c>
       <c r="T47">
-        <v>1.731834504332867</v>
+        <v>1.763905513672365</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.05604557974207044</v>
+        <v>0.05482719757376456</v>
       </c>
       <c r="W47">
-        <v>0.2225844522968198</v>
+        <v>0.2228717468121063</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.2335232489252935</v>
+        <v>0.2284466565573523</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5696,22 +5696,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1964490029279833</v>
+        <v>0.1983490029279834</v>
       </c>
       <c r="C48">
-        <v>14.75192004913674</v>
+        <v>5.923215968379338</v>
       </c>
       <c r="D48">
-        <v>254.4119200491367</v>
+        <v>251.2432159683794</v>
       </c>
       <c r="E48">
-        <v>92.76000000000002</v>
+        <v>98.42000000000004</v>
       </c>
       <c r="F48">
-        <v>260.36</v>
+        <v>266.02</v>
       </c>
       <c r="G48">
         <v>20.7</v>
@@ -5732,37 +5732,37 @@
         <v>14.025</v>
       </c>
       <c r="M48">
-        <v>61.39288800000001</v>
+        <v>62.72751600000001</v>
       </c>
       <c r="N48">
-        <v>-47.36788800000001</v>
+        <v>-48.70251600000001</v>
       </c>
       <c r="O48">
-        <v>-11.36829312</v>
+        <v>-11.68860384</v>
       </c>
       <c r="P48">
-        <v>-35.99959488</v>
+        <v>-37.01391216</v>
       </c>
       <c r="Q48">
-        <v>-16.89959488</v>
+        <v>-17.91391216</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.173940739619286</v>
+        <v>0.1763584894234234</v>
       </c>
       <c r="T48">
-        <v>1.763905513672365</v>
+        <v>1.797186749779391</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.05482719757376456</v>
+        <v>0.05366066145517382</v>
       </c>
       <c r="W48">
-        <v>0.2228717468121063</v>
+        <v>0.22314681602887</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5770,7 +5770,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.2284466565573523</v>
+        <v>0.2235860893965576</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5778,22 +5778,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1983490029279834</v>
+        <v>0.2002490029279833</v>
       </c>
       <c r="C49">
-        <v>5.923215968379338</v>
+        <v>-2.827526615193619</v>
       </c>
       <c r="D49">
-        <v>251.2432159683794</v>
+        <v>248.1524733848064</v>
       </c>
       <c r="E49">
-        <v>98.42000000000004</v>
+        <v>104.08</v>
       </c>
       <c r="F49">
-        <v>266.02</v>
+        <v>271.68</v>
       </c>
       <c r="G49">
         <v>20.7</v>
@@ -5814,37 +5814,37 @@
         <v>14.025</v>
       </c>
       <c r="M49">
-        <v>62.72751600000001</v>
+        <v>64.062144</v>
       </c>
       <c r="N49">
-        <v>-48.70251600000001</v>
+        <v>-50.037144</v>
       </c>
       <c r="O49">
-        <v>-11.68860384</v>
+        <v>-12.00891456</v>
       </c>
       <c r="P49">
-        <v>-37.01391216</v>
+        <v>-38.02822944</v>
       </c>
       <c r="Q49">
-        <v>-17.91391216</v>
+        <v>-18.92822944</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1763584894234234</v>
+        <v>0.1788692296046431</v>
       </c>
       <c r="T49">
-        <v>1.797186749779391</v>
+        <v>1.831748033428994</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.05366066145517382</v>
+        <v>0.05254273100819104</v>
       </c>
       <c r="W49">
-        <v>0.22314681602887</v>
+        <v>0.2234104240282686</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5852,7 +5852,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.2235860893965576</v>
+        <v>0.2189280458674626</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5860,22 +5860,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.2002490029279833</v>
+        <v>0.2021490029279833</v>
       </c>
       <c r="C50">
-        <v>-2.827526615193619</v>
+        <v>-11.50314993610664</v>
       </c>
       <c r="D50">
-        <v>248.1524733848064</v>
+        <v>245.1368500638933</v>
       </c>
       <c r="E50">
-        <v>104.08</v>
+        <v>109.74</v>
       </c>
       <c r="F50">
-        <v>271.68</v>
+        <v>277.34</v>
       </c>
       <c r="G50">
         <v>20.7</v>
@@ -5896,37 +5896,37 @@
         <v>14.025</v>
       </c>
       <c r="M50">
-        <v>64.062144</v>
+        <v>65.396772</v>
       </c>
       <c r="N50">
-        <v>-50.037144</v>
+        <v>-51.371772</v>
       </c>
       <c r="O50">
-        <v>-12.00891456</v>
+        <v>-12.32922528</v>
       </c>
       <c r="P50">
-        <v>-38.02822944</v>
+        <v>-39.04254672</v>
       </c>
       <c r="Q50">
-        <v>-18.92822944</v>
+        <v>-19.94254672</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1788692296046431</v>
+        <v>0.1814784301851263</v>
       </c>
       <c r="T50">
-        <v>1.831748033428994</v>
+        <v>1.867664661535445</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.05254273100819104</v>
+        <v>0.05147043037537082</v>
       </c>
       <c r="W50">
-        <v>0.2234104240282686</v>
+        <v>0.2236632725174876</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.2189280458674626</v>
+        <v>0.2144601265640451</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5942,22 +5942,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.2021490029279833</v>
+        <v>0.2040490029279833</v>
       </c>
       <c r="C51">
-        <v>-11.50314993610664</v>
+        <v>-20.10635972892516</v>
       </c>
       <c r="D51">
-        <v>245.1368500638933</v>
+        <v>242.1936402710749</v>
       </c>
       <c r="E51">
-        <v>109.74</v>
+        <v>115.4</v>
       </c>
       <c r="F51">
-        <v>277.34</v>
+        <v>283</v>
       </c>
       <c r="G51">
         <v>20.7</v>
@@ -5978,37 +5978,37 @@
         <v>14.025</v>
       </c>
       <c r="M51">
-        <v>65.396772</v>
+        <v>66.73140000000001</v>
       </c>
       <c r="N51">
-        <v>-51.371772</v>
+        <v>-52.70640000000001</v>
       </c>
       <c r="O51">
-        <v>-12.32922528</v>
+        <v>-12.649536</v>
       </c>
       <c r="P51">
-        <v>-39.04254672</v>
+        <v>-40.056864</v>
       </c>
       <c r="Q51">
-        <v>-19.94254672</v>
+        <v>-20.956864</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1814784301851263</v>
+        <v>0.1841919987888289</v>
       </c>
       <c r="T51">
-        <v>1.867664661535445</v>
+        <v>1.905017954766154</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.05147043037537082</v>
+        <v>0.05044102176786339</v>
       </c>
       <c r="W51">
-        <v>0.2236632725174876</v>
+        <v>0.2239060070671378</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -6016,7 +6016,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.2144601265640451</v>
+        <v>0.2101709240327642</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -6024,22 +6024,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.2040490029279833</v>
+        <v>0.2059490029279833</v>
       </c>
       <c r="C52">
-        <v>-20.10635972892516</v>
+        <v>-28.63973332540007</v>
       </c>
       <c r="D52">
-        <v>242.1936402710749</v>
+        <v>239.3202666745999</v>
       </c>
       <c r="E52">
-        <v>115.4</v>
+        <v>121.06</v>
       </c>
       <c r="F52">
-        <v>283</v>
+        <v>288.66</v>
       </c>
       <c r="G52">
         <v>20.7</v>
@@ -6060,37 +6060,37 @@
         <v>14.025</v>
       </c>
       <c r="M52">
-        <v>66.73140000000001</v>
+        <v>68.066028</v>
       </c>
       <c r="N52">
-        <v>-52.70640000000001</v>
+        <v>-54.041028</v>
       </c>
       <c r="O52">
-        <v>-12.649536</v>
+        <v>-12.96984672</v>
       </c>
       <c r="P52">
-        <v>-40.056864</v>
+        <v>-41.07118128</v>
       </c>
       <c r="Q52">
-        <v>-20.956864</v>
+        <v>-21.97118128</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1841919987888289</v>
+        <v>0.1870163252947233</v>
       </c>
       <c r="T52">
-        <v>1.905017954766154</v>
+        <v>1.943895872210361</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.05044102176786339</v>
+        <v>0.04945198212535627</v>
       </c>
       <c r="W52">
-        <v>0.2239060070671378</v>
+        <v>0.224139222614841</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.2101709240327642</v>
+        <v>0.2060499255223178</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -6106,22 +6106,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.2059490029279833</v>
+        <v>0.2078490029279833</v>
       </c>
       <c r="C53">
-        <v>-28.63973332540007</v>
+        <v>-37.10572718198557</v>
       </c>
       <c r="D53">
-        <v>239.3202666745999</v>
+        <v>236.5142728180144</v>
       </c>
       <c r="E53">
-        <v>121.06</v>
+        <v>126.72</v>
       </c>
       <c r="F53">
-        <v>288.66</v>
+        <v>294.32</v>
       </c>
       <c r="G53">
         <v>20.7</v>
@@ -6142,37 +6142,37 @@
         <v>14.025</v>
       </c>
       <c r="M53">
-        <v>68.066028</v>
+        <v>69.400656</v>
       </c>
       <c r="N53">
-        <v>-54.041028</v>
+        <v>-55.375656</v>
       </c>
       <c r="O53">
-        <v>-12.96984672</v>
+        <v>-13.29015744</v>
       </c>
       <c r="P53">
-        <v>-41.07118128</v>
+        <v>-42.08549856</v>
       </c>
       <c r="Q53">
-        <v>-21.97118128</v>
+        <v>-22.98549856</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1870163252947233</v>
+        <v>0.1899583320716967</v>
       </c>
       <c r="T53">
-        <v>1.943895872210361</v>
+        <v>1.98439370288141</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.04945198212535627</v>
+        <v>0.04850098246909942</v>
       </c>
       <c r="W53">
-        <v>0.224139222614841</v>
+        <v>0.2243634683337864</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.2060499255223178</v>
+        <v>0.2020874269545809</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -6188,22 +6188,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.2078490029279833</v>
+        <v>0.2097490029279834</v>
       </c>
       <c r="C54">
-        <v>-37.10572718198557</v>
+        <v>-45.50668388394024</v>
       </c>
       <c r="D54">
-        <v>236.5142728180144</v>
+        <v>233.7733161160598</v>
       </c>
       <c r="E54">
-        <v>126.72</v>
+        <v>132.38</v>
       </c>
       <c r="F54">
-        <v>294.32</v>
+        <v>299.98</v>
       </c>
       <c r="G54">
         <v>20.7</v>
@@ -6224,37 +6224,37 @@
         <v>14.025</v>
       </c>
       <c r="M54">
-        <v>69.400656</v>
+        <v>70.73528400000001</v>
       </c>
       <c r="N54">
-        <v>-55.375656</v>
+        <v>-56.71028400000001</v>
       </c>
       <c r="O54">
-        <v>-13.29015744</v>
+        <v>-13.61046816</v>
       </c>
       <c r="P54">
-        <v>-42.08549856</v>
+        <v>-43.09981584000001</v>
       </c>
       <c r="Q54">
-        <v>-22.98549856</v>
+        <v>-23.99981584</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1899583320716967</v>
+        <v>0.1930255306264137</v>
       </c>
       <c r="T54">
-        <v>1.98439370288141</v>
+        <v>2.026614845495909</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.04850098246909942</v>
+        <v>0.04758586959232396</v>
       </c>
       <c r="W54">
-        <v>0.2243634683337864</v>
+        <v>0.22457925195013</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -6262,7 +6262,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.2020874269545809</v>
+        <v>0.1982744566346831</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -6270,22 +6270,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.2097490029279834</v>
+        <v>0.2116490029279833</v>
       </c>
       <c r="C55">
-        <v>-45.50668388394024</v>
+        <v>-53.84483866798428</v>
       </c>
       <c r="D55">
-        <v>233.7733161160598</v>
+        <v>231.0951613320158</v>
       </c>
       <c r="E55">
-        <v>132.38</v>
+        <v>138.04</v>
       </c>
       <c r="F55">
-        <v>299.98</v>
+        <v>305.64</v>
       </c>
       <c r="G55">
         <v>20.7</v>
@@ -6306,37 +6306,37 @@
         <v>14.025</v>
       </c>
       <c r="M55">
-        <v>70.73528400000001</v>
+        <v>72.06991200000002</v>
       </c>
       <c r="N55">
-        <v>-56.71028400000001</v>
+        <v>-58.04491200000002</v>
       </c>
       <c r="O55">
-        <v>-13.61046816</v>
+        <v>-13.93077888</v>
       </c>
       <c r="P55">
-        <v>-43.09981584000001</v>
+        <v>-44.11413312000001</v>
       </c>
       <c r="Q55">
-        <v>-23.99981584</v>
+        <v>-25.01413312000001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1930255306264137</v>
+        <v>0.1962260856400314</v>
       </c>
       <c r="T55">
-        <v>2.026614845495909</v>
+        <v>2.070671689963211</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.04758586959232396</v>
+        <v>0.04670464978505869</v>
       </c>
       <c r="W55">
-        <v>0.22457925195013</v>
+        <v>0.2247870435806832</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.1982744566346831</v>
+        <v>0.1946027074377445</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6352,22 +6352,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2116490029279833</v>
+        <v>0.2135490029279833</v>
       </c>
       <c r="C56">
-        <v>-53.84483866798428</v>
+        <v>-62.12232550168741</v>
       </c>
       <c r="D56">
-        <v>231.0951613320158</v>
+        <v>228.4776744983126</v>
       </c>
       <c r="E56">
-        <v>138.04</v>
+        <v>143.7</v>
       </c>
       <c r="F56">
-        <v>305.64</v>
+        <v>311.3</v>
       </c>
       <c r="G56">
         <v>20.7</v>
@@ -6388,37 +6388,37 @@
         <v>14.025</v>
       </c>
       <c r="M56">
-        <v>72.06991200000002</v>
+        <v>73.40454000000001</v>
       </c>
       <c r="N56">
-        <v>-58.04491200000002</v>
+        <v>-59.37954000000001</v>
       </c>
       <c r="O56">
-        <v>-13.93077888</v>
+        <v>-14.2510896</v>
       </c>
       <c r="P56">
-        <v>-44.11413312000001</v>
+        <v>-45.12845040000001</v>
       </c>
       <c r="Q56">
-        <v>-25.01413312000001</v>
+        <v>-26.02845040000001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1962260856400314</v>
+        <v>0.1995688875431432</v>
       </c>
       <c r="T56">
-        <v>2.070671689963211</v>
+        <v>2.116686616406838</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.04670464978505869</v>
+        <v>0.04585547433442126</v>
       </c>
       <c r="W56">
-        <v>0.2247870435806832</v>
+        <v>0.2249872791519435</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.1946027074377445</v>
+        <v>0.1910644763934219</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6434,22 +6434,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2135490029279833</v>
+        <v>0.2154490029279834</v>
       </c>
       <c r="C57">
-        <v>-62.12232550168741</v>
+        <v>-70.34118275433559</v>
       </c>
       <c r="D57">
-        <v>228.4776744983126</v>
+        <v>225.9188172456645</v>
       </c>
       <c r="E57">
-        <v>143.7</v>
+        <v>149.36</v>
       </c>
       <c r="F57">
-        <v>311.3</v>
+        <v>316.96</v>
       </c>
       <c r="G57">
         <v>20.7</v>
@@ -6470,37 +6470,37 @@
         <v>14.025</v>
       </c>
       <c r="M57">
-        <v>73.40454000000001</v>
+        <v>74.73916800000001</v>
       </c>
       <c r="N57">
-        <v>-59.37954000000001</v>
+        <v>-60.71416800000001</v>
       </c>
       <c r="O57">
-        <v>-14.2510896</v>
+        <v>-14.57140032</v>
       </c>
       <c r="P57">
-        <v>-45.12845040000001</v>
+        <v>-46.14276768000001</v>
       </c>
       <c r="Q57">
-        <v>-26.02845040000001</v>
+        <v>-27.04276768</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1995688875431432</v>
+        <v>0.2030636349873055</v>
       </c>
       <c r="T57">
-        <v>2.116686616406838</v>
+        <v>2.164793130416085</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.04585547433442126</v>
+        <v>0.04503662657844946</v>
       </c>
       <c r="W57">
-        <v>0.2249872791519435</v>
+        <v>0.2251803634528016</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.1910644763934219</v>
+        <v>0.1876526107435394</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6516,22 +6516,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2154490029279834</v>
+        <v>0.2173490029279834</v>
       </c>
       <c r="C58">
-        <v>-70.34118275433559</v>
+        <v>-78.50335849094986</v>
       </c>
       <c r="D58">
-        <v>225.9188172456645</v>
+        <v>223.4166415090502</v>
       </c>
       <c r="E58">
-        <v>149.36</v>
+        <v>155.0200000000001</v>
       </c>
       <c r="F58">
-        <v>316.96</v>
+        <v>322.6200000000001</v>
       </c>
       <c r="G58">
         <v>20.7</v>
@@ -6552,37 +6552,37 @@
         <v>14.025</v>
       </c>
       <c r="M58">
-        <v>74.73916800000001</v>
+        <v>76.07379600000002</v>
       </c>
       <c r="N58">
-        <v>-60.71416800000001</v>
+        <v>-62.04879600000002</v>
       </c>
       <c r="O58">
-        <v>-14.57140032</v>
+        <v>-14.89171104</v>
       </c>
       <c r="P58">
-        <v>-46.14276768000001</v>
+        <v>-47.15708496000001</v>
       </c>
       <c r="Q58">
-        <v>-27.04276768</v>
+        <v>-28.05708496000001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2030636349873055</v>
+        <v>0.2067209288242196</v>
       </c>
       <c r="T58">
-        <v>2.164793130416085</v>
+        <v>2.215137156704831</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.04503662657844946</v>
+        <v>0.04424651032268719</v>
       </c>
       <c r="W58">
-        <v>0.2251803634528016</v>
+        <v>0.2253666728659104</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.1876526107435394</v>
+        <v>0.1843604596778633</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6598,22 +6598,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2173490029279834</v>
+        <v>0.2192490029279834</v>
       </c>
       <c r="C59">
-        <v>-78.50335849094986</v>
+        <v>-86.61071541835426</v>
       </c>
       <c r="D59">
-        <v>223.4166415090502</v>
+        <v>220.9692845816458</v>
       </c>
       <c r="E59">
-        <v>155.0200000000001</v>
+        <v>160.68</v>
       </c>
       <c r="F59">
-        <v>322.6200000000001</v>
+        <v>328.28</v>
       </c>
       <c r="G59">
         <v>20.7</v>
@@ -6634,37 +6634,37 @@
         <v>14.025</v>
       </c>
       <c r="M59">
-        <v>76.07379600000002</v>
+        <v>77.40842400000001</v>
       </c>
       <c r="N59">
-        <v>-62.04879600000002</v>
+        <v>-63.38342400000001</v>
       </c>
       <c r="O59">
-        <v>-14.89171104</v>
+        <v>-15.21202176</v>
       </c>
       <c r="P59">
-        <v>-47.15708496000001</v>
+        <v>-48.17140224000001</v>
       </c>
       <c r="Q59">
-        <v>-28.05708496000001</v>
+        <v>-29.07140224</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2067209288242196</v>
+        <v>0.2105523795105106</v>
       </c>
       <c r="T59">
-        <v>2.215137156704831</v>
+        <v>2.267878517578755</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.04424651032268719</v>
+        <v>0.04348363945505464</v>
       </c>
       <c r="W59">
-        <v>0.2253666728659104</v>
+        <v>0.2255465578164981</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.1843604596778633</v>
+        <v>0.1811818310627277</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6680,22 +6680,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2192490029279833</v>
+        <v>0.2211490029279833</v>
       </c>
       <c r="C60">
-        <v>-86.61071541835415</v>
+        <v>-94.66503550968403</v>
       </c>
       <c r="D60">
-        <v>220.9692845816458</v>
+        <v>218.574964490316</v>
       </c>
       <c r="E60">
-        <v>160.68</v>
+        <v>166.34</v>
       </c>
       <c r="F60">
-        <v>328.28</v>
+        <v>333.94</v>
       </c>
       <c r="G60">
         <v>20.7</v>
@@ -6716,37 +6716,37 @@
         <v>14.025</v>
       </c>
       <c r="M60">
-        <v>77.408424</v>
+        <v>78.74305200000001</v>
       </c>
       <c r="N60">
-        <v>-63.383424</v>
+        <v>-64.718052</v>
       </c>
       <c r="O60">
-        <v>-15.21202176</v>
+        <v>-15.53233248</v>
       </c>
       <c r="P60">
-        <v>-48.17140224</v>
+        <v>-49.18571952</v>
       </c>
       <c r="Q60">
-        <v>-29.07140224</v>
+        <v>-30.08571952</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2105523795105105</v>
+        <v>0.2145707302302791</v>
       </c>
       <c r="T60">
-        <v>2.267878517578755</v>
+        <v>2.323192627763602</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.04348363945505465</v>
+        <v>0.04274662861683338</v>
       </c>
       <c r="W60">
-        <v>0.2255465578164981</v>
+        <v>0.2257203449721507</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6754,7 +6754,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.1811818310627278</v>
+        <v>0.1781109525701392</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6762,22 +6762,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2211490029279833</v>
+        <v>0.2230490029279833</v>
       </c>
       <c r="C61">
-        <v>-94.66503550968403</v>
+        <v>-102.6680243314623</v>
       </c>
       <c r="D61">
-        <v>218.574964490316</v>
+        <v>216.2319756685377</v>
       </c>
       <c r="E61">
-        <v>166.34</v>
+        <v>172</v>
       </c>
       <c r="F61">
-        <v>333.94</v>
+        <v>339.6</v>
       </c>
       <c r="G61">
         <v>20.7</v>
@@ -6798,37 +6798,37 @@
         <v>14.025</v>
       </c>
       <c r="M61">
-        <v>78.74305200000001</v>
+        <v>80.07768</v>
       </c>
       <c r="N61">
-        <v>-64.718052</v>
+        <v>-66.05268000000001</v>
       </c>
       <c r="O61">
-        <v>-15.53233248</v>
+        <v>-15.8526432</v>
       </c>
       <c r="P61">
-        <v>-49.18571952</v>
+        <v>-50.20003680000001</v>
       </c>
       <c r="Q61">
-        <v>-30.08571952</v>
+        <v>-31.10003680000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2145707302302791</v>
+        <v>0.2187899984860361</v>
       </c>
       <c r="T61">
-        <v>2.323192627763602</v>
+        <v>2.381272443457692</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.04274662861683338</v>
+        <v>0.04203418480655283</v>
       </c>
       <c r="W61">
-        <v>0.2257203449721507</v>
+        <v>0.2258883392226148</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.1781109525701392</v>
+        <v>0.17514243669397</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6844,22 +6844,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2230490029279833</v>
+        <v>0.2249490029279833</v>
       </c>
       <c r="C62">
-        <v>-102.6680243314623</v>
+        <v>-110.6213150953265</v>
       </c>
       <c r="D62">
-        <v>216.2319756685377</v>
+        <v>213.9386849046735</v>
       </c>
       <c r="E62">
-        <v>172</v>
+        <v>177.66</v>
       </c>
       <c r="F62">
-        <v>339.6</v>
+        <v>345.26</v>
       </c>
       <c r="G62">
         <v>20.7</v>
@@ -6880,37 +6880,37 @@
         <v>14.025</v>
       </c>
       <c r="M62">
-        <v>80.07768</v>
+        <v>81.412308</v>
       </c>
       <c r="N62">
-        <v>-66.05268000000001</v>
+        <v>-67.38730799999999</v>
       </c>
       <c r="O62">
-        <v>-15.8526432</v>
+        <v>-16.17295392</v>
       </c>
       <c r="P62">
-        <v>-50.20003680000001</v>
+        <v>-51.21435407999999</v>
       </c>
       <c r="Q62">
-        <v>-31.10003680000001</v>
+        <v>-32.11435407999999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2187899984860361</v>
+        <v>0.2232256394728575</v>
       </c>
       <c r="T62">
-        <v>2.381272443457692</v>
+        <v>2.442330711238659</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.04203418480655283</v>
+        <v>0.0413450998097241</v>
       </c>
       <c r="W62">
-        <v>0.2258883392226148</v>
+        <v>0.2260508254648671</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.17514243669397</v>
+        <v>0.1722712492071838</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6926,22 +6926,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2249490029279833</v>
+        <v>0.2268490029279833</v>
       </c>
       <c r="C63">
-        <v>-110.6213150953265</v>
+        <v>-118.5264724546331</v>
       </c>
       <c r="D63">
-        <v>213.9386849046735</v>
+        <v>211.6935275453669</v>
       </c>
       <c r="E63">
-        <v>177.66</v>
+        <v>183.32</v>
       </c>
       <c r="F63">
-        <v>345.26</v>
+        <v>350.92</v>
       </c>
       <c r="G63">
         <v>20.7</v>
@@ -6962,37 +6962,37 @@
         <v>14.025</v>
       </c>
       <c r="M63">
-        <v>81.412308</v>
+        <v>82.74693600000001</v>
       </c>
       <c r="N63">
-        <v>-67.38730799999999</v>
+        <v>-68.721936</v>
       </c>
       <c r="O63">
-        <v>-16.17295392</v>
+        <v>-16.49326464</v>
       </c>
       <c r="P63">
-        <v>-51.21435407999999</v>
+        <v>-52.22867136</v>
       </c>
       <c r="Q63">
-        <v>-32.11435407999999</v>
+        <v>-33.12867136</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2232256394728575</v>
+        <v>0.227894735248459</v>
       </c>
       <c r="T63">
-        <v>2.442330711238659</v>
+        <v>2.506602572060729</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.0413450998097241</v>
+        <v>0.04067824336118016</v>
       </c>
       <c r="W63">
-        <v>0.2260508254648671</v>
+        <v>0.2262080702154337</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -7000,7 +7000,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.1722712492071838</v>
+        <v>0.1694926806715841</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -7008,22 +7008,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2268490029279833</v>
+        <v>0.2287490029279833</v>
       </c>
       <c r="C64">
-        <v>-118.5264724546331</v>
+        <v>-126.3849960644858</v>
       </c>
       <c r="D64">
-        <v>211.6935275453669</v>
+        <v>209.4950039355141</v>
       </c>
       <c r="E64">
-        <v>183.32</v>
+        <v>188.98</v>
       </c>
       <c r="F64">
-        <v>350.92</v>
+        <v>356.58</v>
       </c>
       <c r="G64">
         <v>20.7</v>
@@ -7044,37 +7044,37 @@
         <v>14.025</v>
       </c>
       <c r="M64">
-        <v>82.74693600000001</v>
+        <v>84.081564</v>
       </c>
       <c r="N64">
-        <v>-68.721936</v>
+        <v>-70.05656400000001</v>
       </c>
       <c r="O64">
-        <v>-16.49326464</v>
+        <v>-16.81357536</v>
       </c>
       <c r="P64">
-        <v>-52.22867136</v>
+        <v>-53.24298864000001</v>
       </c>
       <c r="Q64">
-        <v>-33.12867136</v>
+        <v>-34.14298864000001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.227894735248459</v>
+        <v>0.2328162145794984</v>
       </c>
       <c r="T64">
-        <v>2.506602572060729</v>
+        <v>2.57434858752183</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.04067824336118016</v>
+        <v>0.04003255695862174</v>
       </c>
       <c r="W64">
-        <v>0.2262080702154337</v>
+        <v>0.226360323069157</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -7082,7 +7082,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.1694926806715841</v>
+        <v>0.1668023206609238</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -7090,22 +7090,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2287490029279833</v>
+        <v>0.2306490029279833</v>
       </c>
       <c r="C65">
-        <v>-126.3849960644858</v>
+        <v>-134.1983239222106</v>
       </c>
       <c r="D65">
-        <v>209.4950039355141</v>
+        <v>207.3416760777894</v>
       </c>
       <c r="E65">
-        <v>188.98</v>
+        <v>194.64</v>
       </c>
       <c r="F65">
-        <v>356.58</v>
+        <v>362.24</v>
       </c>
       <c r="G65">
         <v>20.7</v>
@@ -7126,37 +7126,37 @@
         <v>14.025</v>
       </c>
       <c r="M65">
-        <v>84.081564</v>
+        <v>85.41619200000001</v>
       </c>
       <c r="N65">
-        <v>-70.05656400000001</v>
+        <v>-71.39119200000002</v>
       </c>
       <c r="O65">
-        <v>-16.81357536</v>
+        <v>-17.13388608</v>
       </c>
       <c r="P65">
-        <v>-53.24298864000001</v>
+        <v>-54.25730592000001</v>
       </c>
       <c r="Q65">
-        <v>-34.14298864000001</v>
+        <v>-35.15730592000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2328162145794984</v>
+        <v>0.238011109428929</v>
       </c>
       <c r="T65">
-        <v>2.57434858752183</v>
+        <v>2.645858270508548</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.04003255695862174</v>
+        <v>0.03940704825614327</v>
       </c>
       <c r="W65">
-        <v>0.226360323069157</v>
+        <v>0.2265078180212014</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -7164,7 +7164,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.1668023206609238</v>
+        <v>0.1641960344005969</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -7172,22 +7172,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2306490029279833</v>
+        <v>0.2325490029279833</v>
       </c>
       <c r="C66">
-        <v>-134.1983239222106</v>
+        <v>-141.9678355039122</v>
       </c>
       <c r="D66">
-        <v>207.3416760777894</v>
+        <v>205.2321644960878</v>
       </c>
       <c r="E66">
-        <v>194.64</v>
+        <v>200.3</v>
       </c>
       <c r="F66">
-        <v>362.24</v>
+        <v>367.9</v>
       </c>
       <c r="G66">
         <v>20.7</v>
@@ -7208,37 +7208,37 @@
         <v>14.025</v>
       </c>
       <c r="M66">
-        <v>85.41619200000001</v>
+        <v>86.75082</v>
       </c>
       <c r="N66">
-        <v>-71.39119200000002</v>
+        <v>-72.72582</v>
       </c>
       <c r="O66">
-        <v>-17.13388608</v>
+        <v>-17.4541968</v>
       </c>
       <c r="P66">
-        <v>-54.25730592000001</v>
+        <v>-55.2716232</v>
       </c>
       <c r="Q66">
-        <v>-35.15730592000001</v>
+        <v>-36.1716232</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.238011109428929</v>
+        <v>0.2435028554126127</v>
       </c>
       <c r="T66">
-        <v>2.645858270508548</v>
+        <v>2.721454221094506</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.03940704825614327</v>
+        <v>0.03880078597527954</v>
       </c>
       <c r="W66">
-        <v>0.2265078180212014</v>
+        <v>0.2266507746670291</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -7246,7 +7246,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.1641960344005969</v>
+        <v>0.1616699415636648</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -7254,22 +7254,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2325490029279833</v>
+        <v>0.2344490029279833</v>
       </c>
       <c r="C67">
-        <v>-141.9678355039122</v>
+        <v>-149.6948547114901</v>
       </c>
       <c r="D67">
-        <v>205.2321644960878</v>
+        <v>203.1651452885099</v>
       </c>
       <c r="E67">
-        <v>200.3</v>
+        <v>205.96</v>
       </c>
       <c r="F67">
-        <v>367.9</v>
+        <v>373.56</v>
       </c>
       <c r="G67">
         <v>20.7</v>
@@ -7290,37 +7290,37 @@
         <v>14.025</v>
       </c>
       <c r="M67">
-        <v>86.75082</v>
+        <v>88.085448</v>
       </c>
       <c r="N67">
-        <v>-72.72582</v>
+        <v>-74.06044800000001</v>
       </c>
       <c r="O67">
-        <v>-17.4541968</v>
+        <v>-17.77450752</v>
       </c>
       <c r="P67">
-        <v>-55.2716232</v>
+        <v>-56.28594048000001</v>
       </c>
       <c r="Q67">
-        <v>-36.1716232</v>
+        <v>-37.18594048000001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2435028554126127</v>
+        <v>0.2493176452776895</v>
       </c>
       <c r="T67">
-        <v>2.721454221094506</v>
+        <v>2.801496992303168</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.03880078597527954</v>
+        <v>0.03821289527868439</v>
       </c>
       <c r="W67">
-        <v>0.2266507746670291</v>
+        <v>0.2267893992932862</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -7328,7 +7328,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.1616699415636648</v>
+        <v>0.1592203969945182</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7336,22 +7336,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2344490029279833</v>
+        <v>0.2363490029279833</v>
       </c>
       <c r="C68">
-        <v>-149.6948547114901</v>
+        <v>-157.3806526433432</v>
       </c>
       <c r="D68">
-        <v>203.1651452885099</v>
+        <v>201.1393473566569</v>
       </c>
       <c r="E68">
-        <v>205.96</v>
+        <v>211.62</v>
       </c>
       <c r="F68">
-        <v>373.56</v>
+        <v>379.22</v>
       </c>
       <c r="G68">
         <v>20.7</v>
@@ -7372,37 +7372,37 @@
         <v>14.025</v>
       </c>
       <c r="M68">
-        <v>88.085448</v>
+        <v>89.42007600000001</v>
       </c>
       <c r="N68">
-        <v>-74.06044800000001</v>
+        <v>-75.39507600000002</v>
       </c>
       <c r="O68">
-        <v>-17.77450752</v>
+        <v>-18.09481824</v>
       </c>
       <c r="P68">
-        <v>-56.28594048000001</v>
+        <v>-57.30025776000002</v>
       </c>
       <c r="Q68">
-        <v>-37.18594048000001</v>
+        <v>-38.20025776000001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2493176452776895</v>
+        <v>0.2554848466497407</v>
       </c>
       <c r="T68">
-        <v>2.801496992303168</v>
+        <v>2.886390840554779</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.03821289527868439</v>
+        <v>0.03764255355810701</v>
       </c>
       <c r="W68">
-        <v>0.2267893992932862</v>
+        <v>0.2269238858709984</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7410,7 +7410,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.1592203969945182</v>
+        <v>0.1568439731587792</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7418,22 +7418,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2363490029279833</v>
+        <v>0.2382490029279833</v>
       </c>
       <c r="C69">
-        <v>-157.3806526433432</v>
+        <v>-165.0264502009469</v>
       </c>
       <c r="D69">
-        <v>201.1393473566569</v>
+        <v>199.1535497990532</v>
       </c>
       <c r="E69">
-        <v>211.62</v>
+        <v>217.2800000000001</v>
       </c>
       <c r="F69">
-        <v>379.22</v>
+        <v>384.8800000000001</v>
       </c>
       <c r="G69">
         <v>20.7</v>
@@ -7454,37 +7454,37 @@
         <v>14.025</v>
       </c>
       <c r="M69">
-        <v>89.42007600000001</v>
+        <v>90.75470400000002</v>
       </c>
       <c r="N69">
-        <v>-75.39507600000002</v>
+        <v>-76.72970400000003</v>
       </c>
       <c r="O69">
-        <v>-18.09481824</v>
+        <v>-18.41512896</v>
       </c>
       <c r="P69">
-        <v>-57.30025776000002</v>
+        <v>-58.31457504000002</v>
       </c>
       <c r="Q69">
-        <v>-38.20025776000001</v>
+        <v>-39.21457504000002</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2554848466497407</v>
+        <v>0.2620374981075451</v>
       </c>
       <c r="T69">
-        <v>2.886390840554779</v>
+        <v>2.976590554322116</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.03764255355810701</v>
+        <v>0.0370889865940172</v>
       </c>
       <c r="W69">
-        <v>0.2269238858709984</v>
+        <v>0.2270544169611308</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7492,7 +7492,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.1568439731587792</v>
+        <v>0.1545374441417382</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7500,22 +7500,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2382490029279833</v>
+        <v>0.2401490029279834</v>
       </c>
       <c r="C70">
-        <v>-165.0264502009469</v>
+        <v>-172.633420542536</v>
       </c>
       <c r="D70">
-        <v>199.1535497990532</v>
+        <v>197.206579457464</v>
       </c>
       <c r="E70">
-        <v>217.2800000000001</v>
+        <v>222.94</v>
       </c>
       <c r="F70">
-        <v>384.8800000000001</v>
+        <v>390.54</v>
       </c>
       <c r="G70">
         <v>20.7</v>
@@ -7536,37 +7536,37 @@
         <v>14.025</v>
       </c>
       <c r="M70">
-        <v>90.75470400000002</v>
+        <v>92.08933200000001</v>
       </c>
       <c r="N70">
-        <v>-76.72970400000003</v>
+        <v>-78.06433200000001</v>
       </c>
       <c r="O70">
-        <v>-18.41512896</v>
+        <v>-18.73543968</v>
       </c>
       <c r="P70">
-        <v>-58.31457504000002</v>
+        <v>-59.32889232000001</v>
       </c>
       <c r="Q70">
-        <v>-39.21457504000002</v>
+        <v>-40.22889232000001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2620374981075451</v>
+        <v>0.2690129012723046</v>
       </c>
       <c r="T70">
-        <v>2.976590554322116</v>
+        <v>3.07260960446154</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.0370889865940172</v>
+        <v>0.03655146504917637</v>
       </c>
       <c r="W70">
-        <v>0.2270544169611308</v>
+        <v>0.2271811645414042</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.1545374441417382</v>
+        <v>0.1522977710382349</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7582,22 +7582,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2401490029279834</v>
+        <v>0.2420490029279833</v>
       </c>
       <c r="C71">
-        <v>-172.633420542536</v>
+        <v>-180.2026913942543</v>
       </c>
       <c r="D71">
-        <v>197.206579457464</v>
+        <v>195.2973086057458</v>
       </c>
       <c r="E71">
-        <v>222.94</v>
+        <v>228.6000000000001</v>
       </c>
       <c r="F71">
-        <v>390.54</v>
+        <v>396.2</v>
       </c>
       <c r="G71">
         <v>20.7</v>
@@ -7618,37 +7618,37 @@
         <v>14.025</v>
       </c>
       <c r="M71">
-        <v>92.08933200000001</v>
+        <v>93.42396000000001</v>
       </c>
       <c r="N71">
-        <v>-78.06433200000001</v>
+        <v>-79.39896000000002</v>
       </c>
       <c r="O71">
-        <v>-18.73543968</v>
+        <v>-19.0557504</v>
       </c>
       <c r="P71">
-        <v>-59.32889232000001</v>
+        <v>-60.34320960000001</v>
       </c>
       <c r="Q71">
-        <v>-40.22889232000001</v>
+        <v>-41.24320960000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2690129012723046</v>
+        <v>0.2764533313147148</v>
       </c>
       <c r="T71">
-        <v>3.07260960446154</v>
+        <v>3.175029924610258</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.03655146504917637</v>
+        <v>0.03602930126275956</v>
       </c>
       <c r="W71">
-        <v>0.2271811645414042</v>
+        <v>0.2273042907622413</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7656,7 +7656,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.1522977710382349</v>
+        <v>0.1501220885948314</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7664,22 +7664,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2420490029279833</v>
+        <v>0.2439490029279833</v>
       </c>
       <c r="C72">
-        <v>-180.2026913942543</v>
+        <v>-187.7353472283378</v>
       </c>
       <c r="D72">
-        <v>195.2973086057458</v>
+        <v>193.4246527716622</v>
       </c>
       <c r="E72">
-        <v>228.6000000000001</v>
+        <v>234.2600000000001</v>
       </c>
       <c r="F72">
-        <v>396.2</v>
+        <v>401.8600000000001</v>
       </c>
       <c r="G72">
         <v>20.7</v>
@@ -7700,37 +7700,37 @@
         <v>14.025</v>
       </c>
       <c r="M72">
-        <v>93.42396000000001</v>
+        <v>94.75858800000002</v>
       </c>
       <c r="N72">
-        <v>-79.39896000000002</v>
+        <v>-80.73358800000003</v>
       </c>
       <c r="O72">
-        <v>-19.0557504</v>
+        <v>-19.37606112000001</v>
       </c>
       <c r="P72">
-        <v>-60.34320960000001</v>
+        <v>-61.35752688000002</v>
       </c>
       <c r="Q72">
-        <v>-41.24320960000001</v>
+        <v>-42.25752688000002</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2764533313147148</v>
+        <v>0.2844068944634981</v>
       </c>
       <c r="T72">
-        <v>3.175029924610258</v>
+        <v>3.28451371511406</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.03602930126275956</v>
+        <v>0.03552184631539675</v>
       </c>
       <c r="W72">
-        <v>0.2273042907622413</v>
+        <v>0.2274239486388294</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.1501220885948314</v>
+        <v>0.1480076929808197</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7746,22 +7746,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2439490029279833</v>
+        <v>0.2458490029279833</v>
       </c>
       <c r="C73">
-        <v>-187.7353472283377</v>
+        <v>-195.2324313171721</v>
       </c>
       <c r="D73">
-        <v>193.4246527716622</v>
+        <v>191.5875686828279</v>
       </c>
       <c r="E73">
-        <v>234.26</v>
+        <v>239.92</v>
       </c>
       <c r="F73">
-        <v>401.86</v>
+        <v>407.52</v>
       </c>
       <c r="G73">
         <v>20.7</v>
@@ -7782,37 +7782,37 @@
         <v>14.025</v>
       </c>
       <c r="M73">
-        <v>94.75858799999999</v>
+        <v>96.093216</v>
       </c>
       <c r="N73">
-        <v>-80.733588</v>
+        <v>-82.06821600000001</v>
       </c>
       <c r="O73">
-        <v>-19.37606112</v>
+        <v>-19.69637184</v>
       </c>
       <c r="P73">
-        <v>-61.35752687999999</v>
+        <v>-62.37184416000001</v>
       </c>
       <c r="Q73">
-        <v>-42.25752687999999</v>
+        <v>-43.27184416000001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.284406894463498</v>
+        <v>0.2929285692657658</v>
       </c>
       <c r="T73">
-        <v>3.284513715114059</v>
+        <v>3.401817776368132</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.03552184631539676</v>
+        <v>0.03502848733879402</v>
       </c>
       <c r="W73">
-        <v>0.2274239486388294</v>
+        <v>0.2275402826855124</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7820,7 +7820,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.1480076929808197</v>
+        <v>0.1459520305783084</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7828,22 +7828,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2458490029279833</v>
+        <v>0.2477490029279834</v>
       </c>
       <c r="C74">
-        <v>-195.2324313171721</v>
+        <v>-202.6949476713983</v>
       </c>
       <c r="D74">
-        <v>191.5875686828279</v>
+        <v>189.7850523286017</v>
       </c>
       <c r="E74">
-        <v>239.92</v>
+        <v>245.58</v>
       </c>
       <c r="F74">
-        <v>407.52</v>
+        <v>413.18</v>
       </c>
       <c r="G74">
         <v>20.7</v>
@@ -7864,37 +7864,37 @@
         <v>14.025</v>
       </c>
       <c r="M74">
-        <v>96.093216</v>
+        <v>97.42784400000001</v>
       </c>
       <c r="N74">
-        <v>-82.06821600000001</v>
+        <v>-83.40284400000002</v>
       </c>
       <c r="O74">
-        <v>-19.69637184</v>
+        <v>-20.01668256</v>
       </c>
       <c r="P74">
-        <v>-62.37184416000001</v>
+        <v>-63.38616144000001</v>
       </c>
       <c r="Q74">
-        <v>-43.27184416000001</v>
+        <v>-44.28616144000001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2929285692657658</v>
+        <v>0.3020814792385719</v>
       </c>
       <c r="T74">
-        <v>3.401817776368132</v>
+        <v>3.527811027344729</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.03502848733879402</v>
+        <v>0.03454864504648178</v>
       </c>
       <c r="W74">
-        <v>0.2275402826855124</v>
+        <v>0.2276534294980396</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.1459520305783084</v>
+        <v>0.143952687693674</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7910,22 +7910,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2477490029279834</v>
+        <v>0.2496490029279833</v>
       </c>
       <c r="C75">
-        <v>-202.6949476713983</v>
+        <v>-210.1238628696331</v>
       </c>
       <c r="D75">
-        <v>189.7850523286017</v>
+        <v>188.0161371303668</v>
       </c>
       <c r="E75">
-        <v>245.58</v>
+        <v>251.24</v>
       </c>
       <c r="F75">
-        <v>413.18</v>
+        <v>418.84</v>
       </c>
       <c r="G75">
         <v>20.7</v>
@@ -7946,37 +7946,37 @@
         <v>14.025</v>
       </c>
       <c r="M75">
-        <v>97.42784400000001</v>
+        <v>98.762472</v>
       </c>
       <c r="N75">
-        <v>-83.40284400000002</v>
+        <v>-84.737472</v>
       </c>
       <c r="O75">
-        <v>-20.01668256</v>
+        <v>-20.33699328</v>
       </c>
       <c r="P75">
-        <v>-63.38616144000001</v>
+        <v>-64.40047872</v>
       </c>
       <c r="Q75">
-        <v>-44.28616144000001</v>
+        <v>-45.30047871999999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3020814792385719</v>
+        <v>0.3119384592092863</v>
       </c>
       <c r="T75">
-        <v>3.527811027344729</v>
+        <v>3.663496066857988</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.03454864504648178</v>
+        <v>0.03408177146477256</v>
       </c>
       <c r="W75">
-        <v>0.2276534294980396</v>
+        <v>0.2277635182886066</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7984,7 +7984,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.143952687693674</v>
+        <v>0.1420073811032191</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7992,22 +7992,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2496490029279833</v>
+        <v>0.2515490029279833</v>
       </c>
       <c r="C76">
-        <v>-210.1238628696331</v>
+        <v>-217.520107786809</v>
       </c>
       <c r="D76">
-        <v>188.0161371303668</v>
+        <v>186.279892213191</v>
       </c>
       <c r="E76">
-        <v>251.24</v>
+        <v>256.9</v>
       </c>
       <c r="F76">
-        <v>418.84</v>
+        <v>424.5</v>
       </c>
       <c r="G76">
         <v>20.7</v>
@@ -8028,37 +8028,37 @@
         <v>14.025</v>
       </c>
       <c r="M76">
-        <v>98.762472</v>
+        <v>100.0971</v>
       </c>
       <c r="N76">
-        <v>-84.737472</v>
+        <v>-86.07210000000001</v>
       </c>
       <c r="O76">
-        <v>-20.33699328</v>
+        <v>-20.657304</v>
       </c>
       <c r="P76">
-        <v>-64.40047872</v>
+        <v>-65.41479600000001</v>
       </c>
       <c r="Q76">
-        <v>-45.30047871999999</v>
+        <v>-46.31479600000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3119384592092863</v>
+        <v>0.3225839975776577</v>
       </c>
       <c r="T76">
-        <v>3.663496066857988</v>
+        <v>3.810035909532309</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.03408177146477256</v>
+        <v>0.03362734784524227</v>
       </c>
       <c r="W76">
-        <v>0.2277635182886066</v>
+        <v>0.2278706713780919</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -8066,7 +8066,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.1420073811032191</v>
+        <v>0.1401139493551761</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -8074,22 +8074,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2515490029279833</v>
+        <v>0.2534490029279833</v>
       </c>
       <c r="C77">
-        <v>-217.520107786809</v>
+        <v>-224.8845792276269</v>
       </c>
       <c r="D77">
-        <v>186.279892213191</v>
+        <v>184.5754207723731</v>
       </c>
       <c r="E77">
-        <v>256.9</v>
+        <v>262.5600000000001</v>
       </c>
       <c r="F77">
-        <v>424.5</v>
+        <v>430.16</v>
       </c>
       <c r="G77">
         <v>20.7</v>
@@ -8110,37 +8110,37 @@
         <v>14.025</v>
       </c>
       <c r="M77">
-        <v>100.0971</v>
+        <v>101.431728</v>
       </c>
       <c r="N77">
-        <v>-86.07210000000001</v>
+        <v>-87.40672800000002</v>
       </c>
       <c r="O77">
-        <v>-20.657304</v>
+        <v>-20.97761472</v>
       </c>
       <c r="P77">
-        <v>-65.41479600000001</v>
+        <v>-66.42911328000001</v>
       </c>
       <c r="Q77">
-        <v>-46.31479600000001</v>
+        <v>-47.32911328000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3225839975776577</v>
+        <v>0.3341166641433934</v>
       </c>
       <c r="T77">
-        <v>3.810035909532309</v>
+        <v>3.968787405762821</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.03362734784524227</v>
+        <v>0.03318488274201539</v>
       </c>
       <c r="W77">
-        <v>0.2278706713780919</v>
+        <v>0.2279750046494328</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -8148,7 +8148,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.1401139493551761</v>
+        <v>0.1382703447583974</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -8156,22 +8156,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2534490029279833</v>
+        <v>0.2553490029279833</v>
       </c>
       <c r="C78">
-        <v>-224.8845792276269</v>
+        <v>-232.2181414711468</v>
       </c>
       <c r="D78">
-        <v>184.5754207723731</v>
+        <v>182.9018585288532</v>
       </c>
       <c r="E78">
-        <v>262.5600000000001</v>
+        <v>268.22</v>
       </c>
       <c r="F78">
-        <v>430.16</v>
+        <v>435.82</v>
       </c>
       <c r="G78">
         <v>20.7</v>
@@ -8192,37 +8192,37 @@
         <v>14.025</v>
       </c>
       <c r="M78">
-        <v>101.431728</v>
+        <v>102.766356</v>
       </c>
       <c r="N78">
-        <v>-87.40672800000002</v>
+        <v>-88.741356</v>
       </c>
       <c r="O78">
-        <v>-20.97761472</v>
+        <v>-21.29792544</v>
       </c>
       <c r="P78">
-        <v>-66.42911328000001</v>
+        <v>-67.44343056</v>
       </c>
       <c r="Q78">
-        <v>-47.32911328000001</v>
+        <v>-48.34343055999999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3341166641433934</v>
+        <v>0.3466521712800628</v>
       </c>
       <c r="T78">
-        <v>3.968787405762821</v>
+        <v>4.141343379926423</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.03318488274201539</v>
+        <v>0.03275391023887234</v>
       </c>
       <c r="W78">
-        <v>0.2279750046494328</v>
+        <v>0.2280766279656739</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.1382703447583974</v>
+        <v>0.1364746259953015</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -8238,22 +8238,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2553490029279833</v>
+        <v>0.2572490029279834</v>
       </c>
       <c r="C79">
-        <v>-232.2181414711468</v>
+        <v>-239.5216277321021</v>
       </c>
       <c r="D79">
-        <v>182.9018585288532</v>
+        <v>181.258372267898</v>
       </c>
       <c r="E79">
-        <v>268.22</v>
+        <v>273.88</v>
       </c>
       <c r="F79">
-        <v>435.82</v>
+        <v>441.48</v>
       </c>
       <c r="G79">
         <v>20.7</v>
@@ -8274,37 +8274,37 @@
         <v>14.025</v>
       </c>
       <c r="M79">
-        <v>102.766356</v>
+        <v>104.100984</v>
       </c>
       <c r="N79">
-        <v>-88.741356</v>
+        <v>-90.07598400000001</v>
       </c>
       <c r="O79">
-        <v>-21.29792544</v>
+        <v>-21.61823616</v>
       </c>
       <c r="P79">
-        <v>-67.44343056</v>
+        <v>-68.45774784</v>
       </c>
       <c r="Q79">
-        <v>-48.34343055999999</v>
+        <v>-49.35774783999999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3466521712800628</v>
+        <v>0.3603272699746111</v>
       </c>
       <c r="T79">
-        <v>4.141343379926423</v>
+        <v>4.329586260832169</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.03275391023887234</v>
+        <v>0.03233398831273294</v>
       </c>
       <c r="W79">
-        <v>0.2280766279656739</v>
+        <v>0.2281756455558576</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -8312,7 +8312,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.1364746259953015</v>
+        <v>0.134724951303054</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8320,22 +8320,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2572490029279834</v>
+        <v>0.2591490029279834</v>
       </c>
       <c r="C80">
-        <v>-239.5216277321021</v>
+        <v>-246.7958415441313</v>
       </c>
       <c r="D80">
-        <v>181.258372267898</v>
+        <v>179.6441584558688</v>
       </c>
       <c r="E80">
-        <v>273.88</v>
+        <v>279.5400000000001</v>
       </c>
       <c r="F80">
-        <v>441.48</v>
+        <v>447.14</v>
       </c>
       <c r="G80">
         <v>20.7</v>
@@ -8356,37 +8356,37 @@
         <v>14.025</v>
       </c>
       <c r="M80">
-        <v>104.100984</v>
+        <v>105.435612</v>
       </c>
       <c r="N80">
-        <v>-90.07598400000001</v>
+        <v>-91.41061200000001</v>
       </c>
       <c r="O80">
-        <v>-21.61823616</v>
+        <v>-21.93854688</v>
       </c>
       <c r="P80">
-        <v>-68.45774784</v>
+        <v>-69.47206512000001</v>
       </c>
       <c r="Q80">
-        <v>-49.35774783999999</v>
+        <v>-50.37206512000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3603272699746111</v>
+        <v>0.3753047590210211</v>
       </c>
       <c r="T80">
-        <v>4.329586260832169</v>
+        <v>4.53575703515751</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.03233398831273294</v>
+        <v>0.03192469732143252</v>
       </c>
       <c r="W80">
-        <v>0.2281756455558576</v>
+        <v>0.2282721563716062</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8394,7 +8394,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.134724951303054</v>
+        <v>0.1330195721726356</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8402,22 +8402,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2591490029279834</v>
+        <v>0.2610490029279833</v>
       </c>
       <c r="C81">
-        <v>-246.7958415441313</v>
+        <v>-254.0415580697513</v>
       </c>
       <c r="D81">
-        <v>179.6441584558688</v>
+        <v>178.0584419302487</v>
       </c>
       <c r="E81">
-        <v>279.5400000000001</v>
+        <v>285.2</v>
       </c>
       <c r="F81">
-        <v>447.14</v>
+        <v>452.8</v>
       </c>
       <c r="G81">
         <v>20.7</v>
@@ -8438,37 +8438,37 @@
         <v>14.025</v>
       </c>
       <c r="M81">
-        <v>105.435612</v>
+        <v>106.77024</v>
       </c>
       <c r="N81">
-        <v>-91.41061200000001</v>
+        <v>-92.74524</v>
       </c>
       <c r="O81">
-        <v>-21.93854688</v>
+        <v>-22.2588576</v>
       </c>
       <c r="P81">
-        <v>-69.47206512000001</v>
+        <v>-70.4863824</v>
       </c>
       <c r="Q81">
-        <v>-50.37206512000001</v>
+        <v>-51.3863824</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3753047590210211</v>
+        <v>0.3917799969720722</v>
       </c>
       <c r="T81">
-        <v>4.53575703515751</v>
+        <v>4.762544886915386</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.03192469732143252</v>
+        <v>0.03152563860491463</v>
       </c>
       <c r="W81">
-        <v>0.2282721563716062</v>
+        <v>0.2283662544169612</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8476,7 +8476,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1330195721726356</v>
+        <v>0.1313568275204776</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8484,22 +8484,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2610490029279833</v>
+        <v>0.2629490029279833</v>
       </c>
       <c r="C82">
-        <v>-254.0415580697513</v>
+        <v>-261.259525341559</v>
       </c>
       <c r="D82">
-        <v>178.0584419302487</v>
+        <v>176.500474658441</v>
       </c>
       <c r="E82">
-        <v>285.2</v>
+        <v>290.86</v>
       </c>
       <c r="F82">
-        <v>452.8</v>
+        <v>458.46</v>
       </c>
       <c r="G82">
         <v>20.7</v>
@@ -8520,37 +8520,37 @@
         <v>14.025</v>
       </c>
       <c r="M82">
-        <v>106.77024</v>
+        <v>108.104868</v>
       </c>
       <c r="N82">
-        <v>-92.74524</v>
+        <v>-94.079868</v>
       </c>
       <c r="O82">
-        <v>-22.2588576</v>
+        <v>-22.57916832</v>
       </c>
       <c r="P82">
-        <v>-70.4863824</v>
+        <v>-71.50069968</v>
       </c>
       <c r="Q82">
-        <v>-51.3863824</v>
+        <v>-52.40069968</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3917799969720722</v>
+        <v>0.4099894704969181</v>
       </c>
       <c r="T82">
-        <v>4.762544886915386</v>
+        <v>5.01320514412146</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.03152563860491463</v>
+        <v>0.03113643319003913</v>
       </c>
       <c r="W82">
-        <v>0.2283662544169612</v>
+        <v>0.2284580290537888</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8558,7 +8558,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.1313568275204776</v>
+        <v>0.1297351382918298</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8566,22 +8566,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2629490029279833</v>
+        <v>0.2648490029279834</v>
       </c>
       <c r="C83">
-        <v>-261.259525341559</v>
+        <v>-268.4504654388363</v>
       </c>
       <c r="D83">
-        <v>176.500474658441</v>
+        <v>174.9695345611638</v>
       </c>
       <c r="E83">
-        <v>290.86</v>
+        <v>296.5200000000001</v>
       </c>
       <c r="F83">
-        <v>458.46</v>
+        <v>464.1200000000001</v>
       </c>
       <c r="G83">
         <v>20.7</v>
@@ -8602,37 +8602,37 @@
         <v>14.025</v>
       </c>
       <c r="M83">
-        <v>108.104868</v>
+        <v>109.439496</v>
       </c>
       <c r="N83">
-        <v>-94.079868</v>
+        <v>-95.41449600000001</v>
       </c>
       <c r="O83">
-        <v>-22.57916832</v>
+        <v>-22.89947904</v>
       </c>
       <c r="P83">
-        <v>-71.50069968</v>
+        <v>-72.51501696000001</v>
       </c>
       <c r="Q83">
-        <v>-52.40069968</v>
+        <v>-53.41501696000001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4099894704969181</v>
+        <v>0.430222218857858</v>
       </c>
       <c r="T83">
-        <v>5.01320514412146</v>
+        <v>5.291716541017096</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.03113643319003913</v>
+        <v>0.0307567205901606</v>
       </c>
       <c r="W83">
-        <v>0.2284580290537888</v>
+        <v>0.2285475652848401</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1297351382918298</v>
+        <v>0.1281530024590026</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8648,22 +8648,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2648490029279834</v>
+        <v>0.2667490029279833</v>
       </c>
       <c r="C84">
-        <v>-268.4504654388363</v>
+        <v>-275.6150756034477</v>
       </c>
       <c r="D84">
-        <v>174.9695345611638</v>
+        <v>173.4649243965524</v>
       </c>
       <c r="E84">
-        <v>296.5200000000001</v>
+        <v>302.1800000000001</v>
       </c>
       <c r="F84">
-        <v>464.1200000000001</v>
+        <v>469.78</v>
       </c>
       <c r="G84">
         <v>20.7</v>
@@ -8684,37 +8684,37 @@
         <v>14.025</v>
       </c>
       <c r="M84">
-        <v>109.439496</v>
+        <v>110.774124</v>
       </c>
       <c r="N84">
-        <v>-95.41449600000001</v>
+        <v>-96.74912400000002</v>
       </c>
       <c r="O84">
-        <v>-22.89947904</v>
+        <v>-23.21978976</v>
       </c>
       <c r="P84">
-        <v>-72.51501696000001</v>
+        <v>-73.52933424000003</v>
       </c>
       <c r="Q84">
-        <v>-53.41501696000001</v>
+        <v>-54.42933424000002</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.430222218857858</v>
+        <v>0.4528352905553792</v>
       </c>
       <c r="T84">
-        <v>5.291716541017096</v>
+        <v>5.602993984606338</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.0307567205901606</v>
+        <v>0.03038615769148397</v>
       </c>
       <c r="W84">
-        <v>0.2285475652848401</v>
+        <v>0.2286349440163481</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8722,7 +8722,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1281530024590026</v>
+        <v>0.1266089903811831</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8730,22 +8730,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2667490029279833</v>
+        <v>0.2686490029279833</v>
       </c>
       <c r="C85">
-        <v>-275.6150756034477</v>
+        <v>-282.7540292986544</v>
       </c>
       <c r="D85">
-        <v>173.4649243965524</v>
+        <v>171.9859707013457</v>
       </c>
       <c r="E85">
-        <v>302.1800000000001</v>
+        <v>307.84</v>
       </c>
       <c r="F85">
-        <v>469.78</v>
+        <v>475.4400000000001</v>
       </c>
       <c r="G85">
         <v>20.7</v>
@@ -8766,37 +8766,37 @@
         <v>14.025</v>
       </c>
       <c r="M85">
-        <v>110.774124</v>
+        <v>112.108752</v>
       </c>
       <c r="N85">
-        <v>-96.74912400000002</v>
+        <v>-98.08375200000003</v>
       </c>
       <c r="O85">
-        <v>-23.21978976</v>
+        <v>-23.54010048000001</v>
       </c>
       <c r="P85">
-        <v>-73.52933424000003</v>
+        <v>-74.54365152000003</v>
       </c>
       <c r="Q85">
-        <v>-54.42933424000002</v>
+        <v>-55.44365152000002</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4528352905553792</v>
+        <v>0.4782749962150904</v>
       </c>
       <c r="T85">
-        <v>5.602993984606338</v>
+        <v>5.953181108644235</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.03038615769148397</v>
+        <v>0.0300244177189663</v>
       </c>
       <c r="W85">
-        <v>0.2286349440163481</v>
+        <v>0.2287202423018677</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1266089903811831</v>
+        <v>0.1251017404956929</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8812,22 +8812,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2686490029279833</v>
+        <v>0.2705490029279833</v>
       </c>
       <c r="C86">
-        <v>-282.7540292986542</v>
+        <v>-289.8679772142196</v>
       </c>
       <c r="D86">
-        <v>171.9859707013457</v>
+        <v>170.5320227857803</v>
       </c>
       <c r="E86">
-        <v>307.84</v>
+        <v>313.5</v>
       </c>
       <c r="F86">
-        <v>475.44</v>
+        <v>481.1</v>
       </c>
       <c r="G86">
         <v>20.7</v>
@@ -8848,37 +8848,37 @@
         <v>14.025</v>
       </c>
       <c r="M86">
-        <v>112.108752</v>
+        <v>113.44338</v>
       </c>
       <c r="N86">
-        <v>-98.083752</v>
+        <v>-99.41837999999998</v>
       </c>
       <c r="O86">
-        <v>-23.54010048</v>
+        <v>-23.86041119999999</v>
       </c>
       <c r="P86">
-        <v>-74.54365152</v>
+        <v>-75.5579688</v>
       </c>
       <c r="Q86">
-        <v>-55.44365152</v>
+        <v>-56.4579688</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4782749962150901</v>
+        <v>0.5071066626294295</v>
       </c>
       <c r="T86">
-        <v>5.953181108644231</v>
+        <v>6.350059849220513</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.03002441771896631</v>
+        <v>0.02967118927521377</v>
       </c>
       <c r="W86">
-        <v>0.2287202423018677</v>
+        <v>0.2288035335689046</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8886,7 +8886,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.125101740495693</v>
+        <v>0.1236299553133907</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8894,22 +8894,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2705490029279833</v>
+        <v>0.2724490029279834</v>
       </c>
       <c r="C87">
-        <v>-289.8679772142196</v>
+        <v>-296.9575482209624</v>
       </c>
       <c r="D87">
-        <v>170.5320227857803</v>
+        <v>169.1024517790376</v>
       </c>
       <c r="E87">
-        <v>313.5</v>
+        <v>319.16</v>
       </c>
       <c r="F87">
-        <v>481.1</v>
+        <v>486.76</v>
       </c>
       <c r="G87">
         <v>20.7</v>
@@ -8930,37 +8930,37 @@
         <v>14.025</v>
       </c>
       <c r="M87">
-        <v>113.44338</v>
+        <v>114.778008</v>
       </c>
       <c r="N87">
-        <v>-99.41837999999998</v>
+        <v>-100.753008</v>
       </c>
       <c r="O87">
-        <v>-23.86041119999999</v>
+        <v>-24.18072192</v>
       </c>
       <c r="P87">
-        <v>-75.5579688</v>
+        <v>-76.57228608</v>
       </c>
       <c r="Q87">
-        <v>-56.4579688</v>
+        <v>-57.47228608</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.5071066626294295</v>
+        <v>0.5400571385315316</v>
       </c>
       <c r="T87">
-        <v>6.350059849220513</v>
+        <v>6.803635552736265</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.02967118927521377</v>
+        <v>0.02932617544643221</v>
       </c>
       <c r="W87">
-        <v>0.2288035335689046</v>
+        <v>0.2288848878297313</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1236299553133907</v>
+        <v>0.1221923976934676</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8976,22 +8976,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2724490029279834</v>
+        <v>0.2743490029279833</v>
       </c>
       <c r="C88">
-        <v>-296.9575482209624</v>
+        <v>-304.0233502776942</v>
       </c>
       <c r="D88">
-        <v>169.1024517790376</v>
+        <v>167.6966497223058</v>
       </c>
       <c r="E88">
-        <v>319.16</v>
+        <v>324.8200000000001</v>
       </c>
       <c r="F88">
-        <v>486.76</v>
+        <v>492.42</v>
       </c>
       <c r="G88">
         <v>20.7</v>
@@ -9012,37 +9012,37 @@
         <v>14.025</v>
       </c>
       <c r="M88">
-        <v>114.778008</v>
+        <v>116.112636</v>
       </c>
       <c r="N88">
-        <v>-100.753008</v>
+        <v>-102.087636</v>
       </c>
       <c r="O88">
-        <v>-24.18072192</v>
+        <v>-24.50103264</v>
       </c>
       <c r="P88">
-        <v>-76.57228608</v>
+        <v>-77.58660336</v>
       </c>
       <c r="Q88">
-        <v>-57.47228608</v>
+        <v>-58.48660336</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.5400571385315316</v>
+        <v>0.5780769184185724</v>
       </c>
       <c r="T88">
-        <v>6.803635552736265</v>
+        <v>7.326992133715977</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.02932617544643221</v>
+        <v>0.02898909297003643</v>
       </c>
       <c r="W88">
-        <v>0.2288848878297313</v>
+        <v>0.2289643718776654</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -9050,7 +9050,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1221923976934676</v>
+        <v>0.1207878873751519</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -9058,22 +9058,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2743490029279833</v>
+        <v>0.2762490029279833</v>
       </c>
       <c r="C89">
-        <v>-304.0233502776942</v>
+        <v>-311.0659712932946</v>
       </c>
       <c r="D89">
-        <v>167.6966497223058</v>
+        <v>166.3140287067054</v>
       </c>
       <c r="E89">
-        <v>324.8200000000001</v>
+        <v>330.48</v>
       </c>
       <c r="F89">
-        <v>492.42</v>
+        <v>498.08</v>
       </c>
       <c r="G89">
         <v>20.7</v>
@@ -9094,37 +9094,37 @@
         <v>14.025</v>
       </c>
       <c r="M89">
-        <v>116.112636</v>
+        <v>117.447264</v>
       </c>
       <c r="N89">
-        <v>-102.087636</v>
+        <v>-103.422264</v>
       </c>
       <c r="O89">
-        <v>-24.50103264</v>
+        <v>-24.82134336</v>
       </c>
       <c r="P89">
-        <v>-77.58660336</v>
+        <v>-78.60092064000001</v>
       </c>
       <c r="Q89">
-        <v>-58.48660336</v>
+        <v>-59.50092064000001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5780769184185724</v>
+        <v>0.6224333282867868</v>
       </c>
       <c r="T89">
-        <v>7.326992133715977</v>
+        <v>7.937574811525642</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.02898909297003643</v>
+        <v>0.02865967145901329</v>
       </c>
       <c r="W89">
-        <v>0.2289643718776654</v>
+        <v>0.2290420494699647</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -9132,7 +9132,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1207878873751519</v>
+        <v>0.1194152977458887</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -9140,22 +9140,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2762490029279833</v>
+        <v>0.2781490029279833</v>
       </c>
       <c r="C90">
-        <v>-311.0659712932946</v>
+        <v>-318.0859799464873</v>
       </c>
       <c r="D90">
-        <v>166.3140287067054</v>
+        <v>164.9540200535127</v>
       </c>
       <c r="E90">
-        <v>330.48</v>
+        <v>336.14</v>
       </c>
       <c r="F90">
-        <v>498.08</v>
+        <v>503.74</v>
       </c>
       <c r="G90">
         <v>20.7</v>
@@ -9176,37 +9176,37 @@
         <v>14.025</v>
       </c>
       <c r="M90">
-        <v>117.447264</v>
+        <v>118.781892</v>
       </c>
       <c r="N90">
-        <v>-103.422264</v>
+        <v>-104.756892</v>
       </c>
       <c r="O90">
-        <v>-24.82134336</v>
+        <v>-25.14165408000001</v>
       </c>
       <c r="P90">
-        <v>-78.60092064000001</v>
+        <v>-79.61523792000001</v>
       </c>
       <c r="Q90">
-        <v>-59.50092064000001</v>
+        <v>-60.51523792000001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.6224333282867868</v>
+        <v>0.6748545399492221</v>
       </c>
       <c r="T90">
-        <v>7.937574811525642</v>
+        <v>8.659172521664338</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.02865967145901329</v>
+        <v>0.02833765267857494</v>
       </c>
       <c r="W90">
-        <v>0.2290420494699647</v>
+        <v>0.229117981498392</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1194152977458887</v>
+        <v>0.1180735528273955</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -9222,22 +9222,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2781490029279833</v>
+        <v>0.2800490029279833</v>
       </c>
       <c r="C91">
-        <v>-318.0859799464873</v>
+        <v>-325.0839264657219</v>
       </c>
       <c r="D91">
-        <v>164.9540200535127</v>
+        <v>163.6160735342781</v>
       </c>
       <c r="E91">
-        <v>336.14</v>
+        <v>341.8000000000001</v>
       </c>
       <c r="F91">
-        <v>503.74</v>
+        <v>509.4</v>
       </c>
       <c r="G91">
         <v>20.7</v>
@@ -9258,37 +9258,37 @@
         <v>14.025</v>
       </c>
       <c r="M91">
-        <v>118.781892</v>
+        <v>120.11652</v>
       </c>
       <c r="N91">
-        <v>-104.756892</v>
+        <v>-106.09152</v>
       </c>
       <c r="O91">
-        <v>-25.14165408000001</v>
+        <v>-25.4619648</v>
       </c>
       <c r="P91">
-        <v>-79.61523792000001</v>
+        <v>-80.6295552</v>
       </c>
       <c r="Q91">
-        <v>-60.51523792000001</v>
+        <v>-61.5295552</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6748545399492221</v>
+        <v>0.7377599939441443</v>
       </c>
       <c r="T91">
-        <v>8.659172521664338</v>
+        <v>9.525089773830771</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.02833765267857494</v>
+        <v>0.02802278987103522</v>
       </c>
       <c r="W91">
-        <v>0.229117981498392</v>
+        <v>0.2291922261484099</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1180735528273955</v>
+        <v>0.1167616244626468</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9304,22 +9304,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2800490029279833</v>
+        <v>0.2819490029279833</v>
       </c>
       <c r="C92">
-        <v>-325.0839264657219</v>
+        <v>-332.0603433714073</v>
       </c>
       <c r="D92">
-        <v>163.6160735342781</v>
+        <v>162.2996566285928</v>
       </c>
       <c r="E92">
-        <v>341.8000000000001</v>
+        <v>347.46</v>
       </c>
       <c r="F92">
-        <v>509.4</v>
+        <v>515.0600000000001</v>
       </c>
       <c r="G92">
         <v>20.7</v>
@@ -9340,37 +9340,37 @@
         <v>14.025</v>
       </c>
       <c r="M92">
-        <v>120.11652</v>
+        <v>121.451148</v>
       </c>
       <c r="N92">
-        <v>-106.09152</v>
+        <v>-107.426148</v>
       </c>
       <c r="O92">
-        <v>-25.4619648</v>
+        <v>-25.78227552</v>
       </c>
       <c r="P92">
-        <v>-80.6295552</v>
+        <v>-81.64387248000001</v>
       </c>
       <c r="Q92">
-        <v>-61.5295552</v>
+        <v>-62.54387248000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.7377599939441443</v>
+        <v>0.8146444377157159</v>
       </c>
       <c r="T92">
-        <v>9.525089773830771</v>
+        <v>10.58343308203419</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.02802278987103522</v>
+        <v>0.02771484712519966</v>
       </c>
       <c r="W92">
-        <v>0.2291922261484099</v>
+        <v>0.2292648390478779</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9378,7 +9378,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1167616244626468</v>
+        <v>0.1154785296883321</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9386,22 +9386,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2819490029279833</v>
+        <v>0.2838490029279833</v>
       </c>
       <c r="C93">
-        <v>-332.0603433714073</v>
+        <v>-339.0157461825991</v>
       </c>
       <c r="D93">
-        <v>162.2996566285928</v>
+        <v>161.004253817401</v>
       </c>
       <c r="E93">
-        <v>347.46</v>
+        <v>353.12</v>
       </c>
       <c r="F93">
-        <v>515.0600000000001</v>
+        <v>520.72</v>
       </c>
       <c r="G93">
         <v>20.7</v>
@@ -9422,37 +9422,37 @@
         <v>14.025</v>
       </c>
       <c r="M93">
-        <v>121.451148</v>
+        <v>122.785776</v>
       </c>
       <c r="N93">
-        <v>-107.426148</v>
+        <v>-108.760776</v>
       </c>
       <c r="O93">
-        <v>-25.78227552</v>
+        <v>-26.10258624</v>
       </c>
       <c r="P93">
-        <v>-81.64387248000001</v>
+        <v>-82.65818976000001</v>
       </c>
       <c r="Q93">
-        <v>-62.54387248000001</v>
+        <v>-63.55818976000001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.8146444377157159</v>
+        <v>0.9107499924301807</v>
       </c>
       <c r="T93">
-        <v>10.58343308203419</v>
+        <v>11.90636221728847</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.02771484712519966</v>
+        <v>0.02741359878688228</v>
       </c>
       <c r="W93">
-        <v>0.2292648390478779</v>
+        <v>0.2293358734060532</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9460,7 +9460,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1154785296883321</v>
+        <v>0.1142233282786761</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9468,22 +9468,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2838490029279833</v>
+        <v>0.2857490029279833</v>
       </c>
       <c r="C94">
-        <v>-339.0157461825991</v>
+        <v>-345.9506340901136</v>
       </c>
       <c r="D94">
-        <v>161.004253817401</v>
+        <v>159.7293659098864</v>
       </c>
       <c r="E94">
-        <v>353.12</v>
+        <v>358.78</v>
       </c>
       <c r="F94">
-        <v>520.72</v>
+        <v>526.38</v>
       </c>
       <c r="G94">
         <v>20.7</v>
@@ -9504,37 +9504,37 @@
         <v>14.025</v>
       </c>
       <c r="M94">
-        <v>122.785776</v>
+        <v>124.120404</v>
       </c>
       <c r="N94">
-        <v>-108.760776</v>
+        <v>-110.095404</v>
       </c>
       <c r="O94">
-        <v>-26.10258624</v>
+        <v>-26.42289696</v>
       </c>
       <c r="P94">
-        <v>-82.65818976000001</v>
+        <v>-83.67250704</v>
       </c>
       <c r="Q94">
-        <v>-63.55818976000001</v>
+        <v>-64.57250704</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.9107499924301807</v>
+        <v>1.034314277063064</v>
       </c>
       <c r="T94">
-        <v>11.90636221728847</v>
+        <v>13.60727110547254</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.02741359878688228</v>
+        <v>0.02711882890745344</v>
       </c>
       <c r="W94">
-        <v>0.2293358734060532</v>
+        <v>0.2294053801436225</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9542,7 +9542,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1142233282786761</v>
+        <v>0.1129951204477228</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9550,22 +9550,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2857490029279833</v>
+        <v>0.2876490029279833</v>
       </c>
       <c r="C95">
-        <v>-345.9506340901136</v>
+        <v>-352.8654905979123</v>
       </c>
       <c r="D95">
-        <v>159.7293659098864</v>
+        <v>158.4745094020878</v>
       </c>
       <c r="E95">
-        <v>358.78</v>
+        <v>364.4400000000001</v>
       </c>
       <c r="F95">
-        <v>526.38</v>
+        <v>532.0400000000001</v>
       </c>
       <c r="G95">
         <v>20.7</v>
@@ -9586,37 +9586,37 @@
         <v>14.025</v>
       </c>
       <c r="M95">
-        <v>124.120404</v>
+        <v>125.455032</v>
       </c>
       <c r="N95">
-        <v>-110.095404</v>
+        <v>-111.430032</v>
       </c>
       <c r="O95">
-        <v>-26.42289696</v>
+        <v>-26.74320768</v>
       </c>
       <c r="P95">
-        <v>-83.67250704</v>
+        <v>-84.68682432000001</v>
       </c>
       <c r="Q95">
-        <v>-64.57250704</v>
+        <v>-65.58682432000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.034314277063064</v>
+        <v>1.199066656573575</v>
       </c>
       <c r="T95">
-        <v>13.60727110547254</v>
+        <v>15.8751496230513</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.02711882890745344</v>
+        <v>0.02683033072758691</v>
       </c>
       <c r="W95">
-        <v>0.2294053801436225</v>
+        <v>0.229473408014435</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9624,7 +9624,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1129951204477228</v>
+        <v>0.1117930446982789</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9632,22 +9632,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2876490029279833</v>
+        <v>0.2895490029279834</v>
       </c>
       <c r="C96">
-        <v>-352.8654905979123</v>
+        <v>-359.760784134489</v>
       </c>
       <c r="D96">
-        <v>158.4745094020878</v>
+        <v>157.239215865511</v>
       </c>
       <c r="E96">
-        <v>364.4400000000001</v>
+        <v>370.1</v>
       </c>
       <c r="F96">
-        <v>532.0400000000001</v>
+        <v>537.7</v>
       </c>
       <c r="G96">
         <v>20.7</v>
@@ -9668,37 +9668,37 @@
         <v>14.025</v>
       </c>
       <c r="M96">
-        <v>125.455032</v>
+        <v>126.78966</v>
       </c>
       <c r="N96">
-        <v>-111.430032</v>
+        <v>-112.76466</v>
       </c>
       <c r="O96">
-        <v>-26.74320768</v>
+        <v>-27.0635184</v>
       </c>
       <c r="P96">
-        <v>-84.68682432000001</v>
+        <v>-85.70114160000001</v>
       </c>
       <c r="Q96">
-        <v>-65.58682432000001</v>
+        <v>-66.60114160000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.199066656573575</v>
+        <v>1.42971998788829</v>
       </c>
       <c r="T96">
-        <v>15.8751496230513</v>
+        <v>19.05017954766157</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.02683033072758691</v>
+        <v>0.02654790619361231</v>
       </c>
       <c r="W96">
-        <v>0.229473408014435</v>
+        <v>0.2295400037195462</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9706,7 +9706,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1117930446982789</v>
+        <v>0.110616275806718</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9714,22 +9714,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2895490029279834</v>
+        <v>0.2914490029279834</v>
       </c>
       <c r="C97">
-        <v>-359.760784134489</v>
+        <v>-366.6369686358853</v>
       </c>
       <c r="D97">
-        <v>157.239215865511</v>
+        <v>156.0230313641147</v>
       </c>
       <c r="E97">
-        <v>370.1</v>
+        <v>375.76</v>
       </c>
       <c r="F97">
-        <v>537.7</v>
+        <v>543.36</v>
       </c>
       <c r="G97">
         <v>20.7</v>
@@ -9750,37 +9750,37 @@
         <v>14.025</v>
       </c>
       <c r="M97">
-        <v>126.78966</v>
+        <v>128.124288</v>
       </c>
       <c r="N97">
-        <v>-112.76466</v>
+        <v>-114.099288</v>
       </c>
       <c r="O97">
-        <v>-27.0635184</v>
+        <v>-27.38382912</v>
       </c>
       <c r="P97">
-        <v>-85.70114160000001</v>
+        <v>-86.71545888</v>
       </c>
       <c r="Q97">
-        <v>-66.60114160000001</v>
+        <v>-67.61545888000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.42971998788829</v>
+        <v>1.775699984860364</v>
       </c>
       <c r="T97">
-        <v>19.05017954766157</v>
+        <v>23.81272443457697</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.02654790619361231</v>
+        <v>0.02627136550409552</v>
       </c>
       <c r="W97">
-        <v>0.2295400037195462</v>
+        <v>0.2296052120141343</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9788,7 +9788,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.110616275806718</v>
+        <v>0.1094640229337314</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9796,22 +9796,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2914490029279834</v>
+        <v>0.2933490029279833</v>
       </c>
       <c r="C98">
-        <v>-366.6369686358853</v>
+        <v>-373.4944841018557</v>
       </c>
       <c r="D98">
-        <v>156.0230313641147</v>
+        <v>154.8255158981443</v>
       </c>
       <c r="E98">
-        <v>375.76</v>
+        <v>381.42</v>
       </c>
       <c r="F98">
-        <v>543.36</v>
+        <v>549.02</v>
       </c>
       <c r="G98">
         <v>20.7</v>
@@ -9832,37 +9832,37 @@
         <v>14.025</v>
       </c>
       <c r="M98">
-        <v>128.124288</v>
+        <v>129.458916</v>
       </c>
       <c r="N98">
-        <v>-114.099288</v>
+        <v>-115.433916</v>
       </c>
       <c r="O98">
-        <v>-27.38382912</v>
+        <v>-27.70413984</v>
       </c>
       <c r="P98">
-        <v>-86.71545888</v>
+        <v>-87.72977615999999</v>
       </c>
       <c r="Q98">
-        <v>-67.61545888000001</v>
+        <v>-68.62977615999998</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.775699984860359</v>
+        <v>2.352333313147145</v>
       </c>
       <c r="T98">
-        <v>23.81272443457691</v>
+        <v>31.75029924610254</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.02627136550409552</v>
+        <v>0.02600052668446567</v>
       </c>
       <c r="W98">
-        <v>0.2296052120141343</v>
+        <v>0.229669075807803</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9870,7 +9870,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1094640229337314</v>
+        <v>0.1083355278519403</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9878,22 +9878,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2933490029279833</v>
+        <v>0.2952490029279833</v>
       </c>
       <c r="C99">
-        <v>-373.4944841018557</v>
+        <v>-380.3337571266165</v>
       </c>
       <c r="D99">
-        <v>154.8255158981443</v>
+        <v>153.6462428733834</v>
       </c>
       <c r="E99">
-        <v>381.42</v>
+        <v>387.0799999999999</v>
       </c>
       <c r="F99">
-        <v>549.02</v>
+        <v>554.6799999999999</v>
       </c>
       <c r="G99">
         <v>20.7</v>
@@ -9914,37 +9914,37 @@
         <v>14.025</v>
       </c>
       <c r="M99">
-        <v>129.458916</v>
+        <v>130.793544</v>
       </c>
       <c r="N99">
-        <v>-115.433916</v>
+        <v>-116.768544</v>
       </c>
       <c r="O99">
-        <v>-27.70413984</v>
+        <v>-28.02445056</v>
       </c>
       <c r="P99">
-        <v>-87.72977615999999</v>
+        <v>-88.74409344</v>
       </c>
       <c r="Q99">
-        <v>-68.62977615999998</v>
+        <v>-69.64409344000001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.352333313147145</v>
+        <v>3.505599969720718</v>
       </c>
       <c r="T99">
-        <v>31.75029924610254</v>
+        <v>47.62544886915381</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.02600052668446567</v>
+        <v>0.02573521518768541</v>
       </c>
       <c r="W99">
-        <v>0.229669075807803</v>
+        <v>0.2297316362587438</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9952,7 +9952,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1083355278519403</v>
+        <v>0.1072300632820226</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9960,22 +9960,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2952490029279833</v>
+        <v>0.2971490029279834</v>
       </c>
       <c r="C100">
-        <v>-380.3337571266165</v>
+        <v>-387.1552014055226</v>
       </c>
       <c r="D100">
-        <v>153.6462428733834</v>
+        <v>152.4847985944774</v>
       </c>
       <c r="E100">
-        <v>387.0799999999999</v>
+        <v>392.74</v>
       </c>
       <c r="F100">
-        <v>554.6799999999999</v>
+        <v>560.34</v>
       </c>
       <c r="G100">
         <v>20.7</v>
@@ -9996,37 +9996,37 @@
         <v>14.025</v>
       </c>
       <c r="M100">
-        <v>130.793544</v>
+        <v>132.128172</v>
       </c>
       <c r="N100">
-        <v>-116.768544</v>
+        <v>-118.103172</v>
       </c>
       <c r="O100">
-        <v>-28.02445056</v>
+        <v>-28.34476128</v>
       </c>
       <c r="P100">
-        <v>-88.74409344</v>
+        <v>-89.75841072</v>
       </c>
       <c r="Q100">
-        <v>-69.64409344000001</v>
+        <v>-70.65841072000001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.505599969720718</v>
+        <v>6.965399939441436</v>
       </c>
       <c r="T100">
-        <v>47.62544886915381</v>
+        <v>95.25089773830763</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.02573521518768541</v>
+        <v>0.02547526351912293</v>
       </c>
       <c r="W100">
-        <v>0.2297316362587438</v>
+        <v>0.2297929328621908</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -10034,91 +10034,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1072300632820226</v>
+        <v>0.1061469313296789</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2971490029279834</v>
-      </c>
-      <c r="C101">
-        <v>-387.1552014055226</v>
-      </c>
-      <c r="D101">
-        <v>152.4847985944774</v>
-      </c>
-      <c r="E101">
-        <v>392.74</v>
-      </c>
-      <c r="F101">
-        <v>560.34</v>
-      </c>
-      <c r="G101">
-        <v>20.7</v>
-      </c>
-      <c r="H101">
-        <v>398.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>33.125</v>
-      </c>
-      <c r="K101">
-        <v>19.1</v>
-      </c>
-      <c r="L101">
-        <v>14.025</v>
-      </c>
-      <c r="M101">
-        <v>132.128172</v>
-      </c>
-      <c r="N101">
-        <v>-118.103172</v>
-      </c>
-      <c r="O101">
-        <v>-28.34476128</v>
-      </c>
-      <c r="P101">
-        <v>-89.75841072</v>
-      </c>
-      <c r="Q101">
-        <v>-70.65841072000001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.965399939441436</v>
-      </c>
-      <c r="T101">
-        <v>95.25089773830763</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.02547526351912293</v>
-      </c>
-      <c r="W101">
-        <v>0.2297929328621908</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1061469313296789</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
